--- a/input.xlsx
+++ b/input.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ID0346943\Downloads\url-auditor-automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33DDB4B2-CD76-48D1-82E2-E99BC9D5C1BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3046708-43BF-4602-9536-51FEB68A4BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{26AC8650-8AEB-4038-81FB-D121AD67B51D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$51</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="168">
   <si>
     <t>Country</t>
   </si>
@@ -65,34 +68,19 @@
     <t>Comparision</t>
   </si>
   <si>
-    <t>Bolivia</t>
-  </si>
-  <si>
     <t>Voter Info Website</t>
   </si>
   <si>
-    <t>viw-000A03502141DF0ED4F11AC7D42AAB7B</t>
-  </si>
-  <si>
     <t>voting-requirements</t>
   </si>
   <si>
     <t>Spanish</t>
   </si>
   <si>
-    <t>https://web.oep.org.bo/elecciones-subnacionales-2026/peb-eg-2026/</t>
-  </si>
-  <si>
     <t>Inactive</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>Estonia</t>
-  </si>
-  <si>
-    <t>viw-005B0EFB330BB300088A2DCF9D97BA47</t>
+    <t>Same</t>
   </si>
   <si>
     <t>voting-dates</t>
@@ -101,451 +89,460 @@
     <t>English</t>
   </si>
   <si>
-    <t>https://www.valimised.ee/en/parliamentary-elections-2023/parliamentary-elections-2023</t>
-  </si>
-  <si>
     <t>Active</t>
   </si>
   <si>
-    <t>Russian</t>
-  </si>
-  <si>
-    <t>https://www.valimised.ee/ru/vybory-v-riygikogu-2023/vybory-v-riygikogu-5-marta-2023-g</t>
-  </si>
-  <si>
-    <t>Estonian</t>
-  </si>
-  <si>
-    <t>https://www.valimised.ee/et/riigikogu-valimised-2023/riigikogu-valimised-2023</t>
-  </si>
-  <si>
-    <t>Moldova</t>
-  </si>
-  <si>
-    <t>viw-0080FBCFC7B1D79C504B3C4466E14B2E</t>
-  </si>
-  <si>
     <t>voting-id-requirements</t>
   </si>
   <si>
-    <t>https://www.voteaza.md/ru/chasto-zadavaemye-voprosy/#1529386641918-0e3927fa-67ff</t>
-  </si>
-  <si>
     <t>Lithuania</t>
   </si>
   <si>
-    <t>viw-00C732DE3F81DBB850B1487C253A1798</t>
-  </si>
-  <si>
     <t>polling-place-hours</t>
   </si>
   <si>
-    <t>https://www.vrk.lt/en/balsavimas-rinkimu-diena-2024-sei</t>
-  </si>
-  <si>
     <t>Lithuanian</t>
   </si>
   <si>
-    <t>https://www.vrk.lt/balsavimas-rinkimu-diena-2024-sei</t>
-  </si>
-  <si>
-    <t>Poland</t>
-  </si>
-  <si>
-    <t>viw-0110309E6918B7668F6AB82900E601E1</t>
-  </si>
-  <si>
     <t>polling-location</t>
   </si>
   <si>
-    <t>https://wybory.gov.pl/prezydent2025/en/obwodowe/wyszukiwarka</t>
-  </si>
-  <si>
-    <t>Polish</t>
-  </si>
-  <si>
-    <t>https://wybory.gov.pl/prezydent2025/pl/obwodowe/wyszukiwarka/1</t>
-  </si>
-  <si>
-    <t>Romania</t>
-  </si>
-  <si>
-    <t>viw-0113DAE669EE7B87721CF64147CD6FB9</t>
-  </si>
-  <si>
     <t>how-to-vote</t>
   </si>
   <si>
-    <t>Romanian</t>
-  </si>
-  <si>
-    <t>https://www.roaep.ro/prezentare/accesibilitate/</t>
-  </si>
-  <si>
-    <t>viw-01267302E24B915161BE4EFCEC17D3F2</t>
-  </si>
-  <si>
-    <t>how-to-vote-military</t>
-  </si>
-  <si>
-    <t>https://www.legis.md/cautare/getResults?doc_id=149860&amp;lang=ro</t>
-  </si>
-  <si>
-    <t>Brazil</t>
-  </si>
-  <si>
-    <t>viw-012C80ED0612E25B649B43FB8424CD18</t>
-  </si>
-  <si>
-    <t>how-to-vote-overseas</t>
+    <t>Changed</t>
   </si>
   <si>
     <t>Portuguese</t>
   </si>
   <si>
-    <t>https://www.tse.jus.br/legislacao/compilada/res/2026/resolucao-no-23-751-de-26-de-fevereiro-de-2026</t>
-  </si>
-  <si>
-    <t>Czech Republic</t>
-  </si>
-  <si>
-    <t>viw-01515CF2E9A7B50B609DD07FD232BD80</t>
-  </si>
-  <si>
     <t>election-results-information</t>
   </si>
   <si>
-    <t>https://www.volby.cz/index_en.htm</t>
-  </si>
-  <si>
-    <t>Czech</t>
-  </si>
-  <si>
-    <t>https://www.volby.cz/index.htm</t>
-  </si>
-  <si>
-    <t>Tunisia</t>
-  </si>
-  <si>
-    <t>viw-0154FE368AA64FE77AB1B8DE0ADB3309</t>
-  </si>
-  <si>
     <t>candidate-information</t>
   </si>
   <si>
     <t>French</t>
   </si>
   <si>
-    <t>https://www.isie.tn/presidentielle-2024-la-liste-finale-des-candidats/</t>
-  </si>
-  <si>
-    <t>Jamaica</t>
-  </si>
-  <si>
-    <t>viw-018030C436AD9038BDBD0113EC68609E</t>
-  </si>
-  <si>
     <t>voter-registration-deadlines</t>
   </si>
   <si>
-    <t>https://www.ecj.com.jm/</t>
-  </si>
-  <si>
     <t>France</t>
   </si>
   <si>
-    <t>viw-01A7EA19BE846B2775B15F1FAC808BBC</t>
-  </si>
-  <si>
     <t>voter-registration-by-mail</t>
   </si>
   <si>
-    <t>https://www.diplomatie.gouv.fr/fr/services-aux-francaises-et-aux-francais/vie-administrative-et-elections/modalites-de-vote/vote-par-correspondance?</t>
-  </si>
-  <si>
-    <t>Albania</t>
-  </si>
-  <si>
-    <t>viw-01AB9AB2D7C00D844D088CADF4C2BE8D</t>
-  </si>
-  <si>
-    <t>Albanian</t>
-  </si>
-  <si>
-    <t>https://iemis-kqz.com/results2025/?lang=AL&amp;v1=IN</t>
-  </si>
-  <si>
-    <t>viw-01BD25995C66855028D91938D81FCAC0</t>
-  </si>
-  <si>
-    <t>https://www.oep.org.bo/elecciones-generales-2025/nacional-2025/</t>
-  </si>
-  <si>
     <t>Ghana</t>
   </si>
   <si>
-    <t>viw-01C604571E8F9FC87216992C79089BC9</t>
-  </si>
-  <si>
     <t>voting-procedures</t>
   </si>
   <si>
-    <t>https://ec.gov.gh/voting/</t>
-  </si>
-  <si>
-    <t>Croatia</t>
-  </si>
-  <si>
-    <t>viw-01C7D32C44D0BF5E45311381FBFC0F78</t>
-  </si>
-  <si>
-    <t>Croatian</t>
-  </si>
-  <si>
-    <t>https://www.izbori.hr/site/izbori-referendumi/izbori-za-predsjednika-republike-hrvatske/66</t>
-  </si>
-  <si>
-    <t>Senegal</t>
-  </si>
-  <si>
-    <t>viw-01EE09EEA4A536D221EBC859107CB207</t>
-  </si>
-  <si>
     <t>where-to-register-to-vote</t>
   </si>
   <si>
-    <t>https://primature.sn/publications/lois-et-reglements/code-electoral-0</t>
-  </si>
-  <si>
     <t>Cape Verde</t>
   </si>
   <si>
-    <t>viw-020CE51BF545E63CA410D728266069E7</t>
-  </si>
-  <si>
-    <t>https://dgape.cv/formas-de-votar/</t>
-  </si>
-  <si>
     <t>Nigeria</t>
   </si>
   <si>
-    <t>viw-021D31BC5B70C3FA1A8784076D352FBC</t>
-  </si>
-  <si>
-    <t>https://www.inecnigeria.org/upcoming-elections/</t>
-  </si>
-  <si>
-    <t>Germany</t>
-  </si>
-  <si>
-    <t>viw-022906C595408E3A05EF9DCD309574BD</t>
-  </si>
-  <si>
-    <t>https://www.bundeswahlleiterin.de/en/service/glossar/w/wahlzeit.html?utm_source</t>
-  </si>
-  <si>
-    <t>German</t>
-  </si>
-  <si>
-    <t>https://www.bundeswahlleiterin.de/service/glossar/w/wahlzeit.html</t>
-  </si>
-  <si>
-    <t>Malta</t>
-  </si>
-  <si>
-    <t>viw-0231FF28D9D6F36BB6AEECD4E9ED1E58</t>
-  </si>
-  <si>
     <t>polling-place-early</t>
   </si>
   <si>
-    <t>https://electoral.gov.mt/Contents/Item/Display/81120</t>
-  </si>
-  <si>
-    <t>Maltese</t>
-  </si>
-  <si>
-    <t>https://electoral.gov.mt/pr2-17-05-26-mt</t>
-  </si>
-  <si>
-    <t>Indonesia</t>
-  </si>
-  <si>
-    <t>viw-025819B197A083A115B3569A375693D8</t>
-  </si>
-  <si>
     <t>how-to-vote-absentee</t>
   </si>
   <si>
-    <t>Bahasa Indonesia</t>
-  </si>
-  <si>
-    <t>https://www.kpu.go.id/page/read/1137/bagaimana-cara-memilih-pada-pemilu-2024</t>
-  </si>
-  <si>
-    <t>South Africa</t>
-  </si>
-  <si>
-    <t>viw-027077FA254B9ECA149AB78F0885B394</t>
-  </si>
-  <si>
-    <t>https://www.elections.org.za/pw/voter/voter-education</t>
-  </si>
-  <si>
-    <t>viw-02A255A2B33FF184F2A08DE036FA90EF</t>
-  </si>
-  <si>
-    <t>https://www.elections.org.za/pw/SpecialVotes/About-Special-Vote</t>
-  </si>
-  <si>
-    <t>viw-02E5D42F64D89CBFE9541DF07B3E5E38</t>
-  </si>
-  <si>
-    <t>https://www.bundeswahlleiterin.de/en/bundestagswahlen/2025/termine.html</t>
-  </si>
-  <si>
-    <t>https://www.bundeswahlleiterin.de/bundestagswahlen/2025/termine.html</t>
-  </si>
-  <si>
-    <t>Mauritius</t>
-  </si>
-  <si>
-    <t>viw-02EF851676EAEFBA8AA91089106CD299</t>
-  </si>
-  <si>
-    <t>https://electoral.govmu.org/oec/?page_id=669#</t>
-  </si>
-  <si>
-    <t>Greece</t>
-  </si>
-  <si>
-    <t>viw-02FCBE35E7438BE4D94AD5ECD77FF155</t>
-  </si>
-  <si>
     <t>voting-accessibility</t>
   </si>
   <si>
-    <t>Greek</t>
-  </si>
-  <si>
-    <t>https://www.ypes.gr/diefkriniseis-gia-ti-diefkolynsi-atomon-me-anapiria-stin-askisi-tou-eklogikou-tous-dikaiomatos/</t>
-  </si>
-  <si>
-    <t>United Kingdom</t>
-  </si>
-  <si>
-    <t>viw-030AD0160C53C1E55FEE92F49D00A8B8</t>
-  </si>
-  <si>
-    <t>https://www.gov.uk/how-to-vote/voting-in-person</t>
-  </si>
-  <si>
-    <t>Bhutan</t>
-  </si>
-  <si>
-    <t>viw-0316E4214EA791A21F76C9879610D836</t>
-  </si>
-  <si>
     <t>voter-registration-check</t>
   </si>
   <si>
-    <t>https://berms.ecb.bt/enrollment/check</t>
-  </si>
-  <si>
-    <t>Australia</t>
-  </si>
-  <si>
-    <t>viw-03255572D90FA02871117E11904B0B3E</t>
-  </si>
-  <si>
     <t>polling-place-mail</t>
   </si>
   <si>
-    <t>https://aec.gov.au/community/accessible-education-how.htm?utm</t>
-  </si>
-  <si>
     <t>Canada</t>
   </si>
   <si>
-    <t>viw-0335CD0C3D378D50626B97AC7925F25B</t>
-  </si>
-  <si>
     <t>voter-registration</t>
   </si>
   <si>
-    <t>https://ereg.elections.ca/en/ereg/index</t>
-  </si>
-  <si>
-    <t>https://ereg.elections.ca/fr/ereg/index</t>
-  </si>
-  <si>
-    <t>viw-034515CC8533E1639A6B42B6EC10556E</t>
-  </si>
-  <si>
     <t>https://www.inecnigeria.org/what-happens-on-election-day/</t>
   </si>
   <si>
-    <t>viw-034FB3D409F70FA45CCF91331117C2CB</t>
-  </si>
-  <si>
-    <t>https://www.ecj.com.jm/elections/other-information/nomination-paper/page/2/</t>
-  </si>
-  <si>
-    <t>Cyprus</t>
-  </si>
-  <si>
-    <t>viw-03A0CF76B14B0B8B8FFFBC69232C007D</t>
-  </si>
-  <si>
-    <t>https://live.elections.moi.gov.cy/</t>
-  </si>
-  <si>
-    <t>North Macedonia</t>
-  </si>
-  <si>
-    <t>viw-03B6E6EEA48EEB173E8EBC0A42F79D5D</t>
-  </si>
-  <si>
-    <t>https://www.sec.mk/sq/edukacija-parlamentarni-izbori-2020/</t>
-  </si>
-  <si>
-    <t>Macedonian</t>
-  </si>
-  <si>
-    <t>https://www.sec.mk/edukacija-parlamentarni-izbori-2020/</t>
-  </si>
-  <si>
-    <t>viw-03C0AF0BE5A5BDB3DD30C26061107555</t>
-  </si>
-  <si>
-    <t>https://www.ecb.bt/naelections2023-24notifications/</t>
-  </si>
-  <si>
-    <t>Mexico</t>
-  </si>
-  <si>
-    <t>viw-045698D9F1C6F5D29A571DDD966CBE82</t>
-  </si>
-  <si>
     <t>registration-requirements</t>
   </si>
   <si>
-    <t>https://ine.mx/credencial/documentos-necesarios/</t>
-  </si>
-  <si>
     <t>Israel</t>
   </si>
   <si>
-    <t>viw-0467D8819BDD15DB6AFB8A93CDBE8C62</t>
-  </si>
-  <si>
-    <t>https://www.gov.il/en/pages/tz_elections</t>
-  </si>
-  <si>
     <t>Arabic</t>
   </si>
   <si>
-    <t>https://www.gov.il/ar/pages/tz_elections</t>
+    <t>Hebrew</t>
+  </si>
+  <si>
+    <t>Italian</t>
+  </si>
+  <si>
+    <t>Hungary</t>
+  </si>
+  <si>
+    <t>Hungarian</t>
+  </si>
+  <si>
+    <t>Slovenia</t>
+  </si>
+  <si>
+    <t>viw-05C94A9EA8121545028563C8993959EE</t>
+  </si>
+  <si>
+    <t>https://www.dvk-rs.si/it/istruzione-elettorale/</t>
+  </si>
+  <si>
+    <t>Slovenian</t>
+  </si>
+  <si>
+    <t>https://www.dvk-rs.si/izobrazevanje-o-volitvah/</t>
+  </si>
+  <si>
+    <t>viw-05F313F27EBEED17E6C6356093EA3005</t>
+  </si>
+  <si>
+    <t>https://www.inecnigeria.org/footer-faqs/why-cant-the-registration-of-voters-exercise-continue-till-a-week-before-the-date-of-election/</t>
+  </si>
+  <si>
+    <t>Zambia</t>
+  </si>
+  <si>
+    <t>viw-061183A226A0BFDDB4CC02378CF0B1DA</t>
+  </si>
+  <si>
+    <t>https://www.elections.org.zm/verc/pollactivities.php</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t>viw-061B06290DD5D6D39D0C9C6EE6D0AACD</t>
+  </si>
+  <si>
+    <t>Dutch</t>
+  </si>
+  <si>
+    <t>https://waarismijnstemlokaal.nl/</t>
+  </si>
+  <si>
+    <t>viw-06651F7EE2538F75DC139A5BD884624B</t>
+  </si>
+  <si>
+    <t>https://www.service-public.fr/particuliers/actualites/A14943?lang=en</t>
+  </si>
+  <si>
+    <t>https://www.service-public.fr/particuliers/actualites/A14943</t>
+  </si>
+  <si>
+    <t>South Korea</t>
+  </si>
+  <si>
+    <t>viw-067D2CB8B43358805FBADCC579D73CF4</t>
+  </si>
+  <si>
+    <t>https://www.nec.go.kr/site/eng/03/10301100000002020070601.jsp</t>
+  </si>
+  <si>
+    <t>Singapore</t>
+  </si>
+  <si>
+    <t>viw-0694CA65FD3711733081518B76012D69</t>
+  </si>
+  <si>
+    <t>https://www.eld.gov.sg/candidate_prospective.html</t>
+  </si>
+  <si>
+    <t>viw-06DBBA4FE2CA66DB8CAD86E0B3F3B229</t>
+  </si>
+  <si>
+    <t>https://e-seimas.lrs.lt/rs/legalact/TAD/e8906340104611e5b0d3e1beb7dd5516/</t>
+  </si>
+  <si>
+    <t>viw-071B566D8908A5C1A2229F29DD949F32</t>
+  </si>
+  <si>
+    <t>https://cne.cv/apoio-ao-leitor/</t>
+  </si>
+  <si>
+    <t>viw-075E7E22620D1340FB3F7B8CDA4877DA</t>
+  </si>
+  <si>
+    <t>voter-info</t>
+  </si>
+  <si>
+    <t>https://www.elections.ca/scripts/vis/FindED?L=e&amp;PAGEID=20</t>
+  </si>
+  <si>
+    <t>https://www.elections.ca/scripts/vis/FindED?L=f&amp;PAGEID=20</t>
+  </si>
+  <si>
+    <t>viw-07D561D555AFDD3F1219605568F209E1</t>
+  </si>
+  <si>
+    <t>https://www.valasztas.hu/en/kinek-van-valasztojoga-</t>
+  </si>
+  <si>
+    <t>https://www.valasztas.hu/kinek-van-valasztojoga-</t>
+  </si>
+  <si>
+    <t>viw-083E67ECFB03D53ABE9E392B6EE85F82</t>
+  </si>
+  <si>
+    <t>https://www.gov.il/en/pages/knesset25-elections-info?chapterIndex=12</t>
+  </si>
+  <si>
+    <t>https://www.gov.il/ar/pages/knesset25-elections-info</t>
+  </si>
+  <si>
+    <t>https://www.gov.il/he/pages/knesset25-elections-info</t>
+  </si>
+  <si>
+    <t>Finland</t>
+  </si>
+  <si>
+    <t>viw-0840052137CAC04AE2EE7B55DD923046</t>
+  </si>
+  <si>
+    <t>https://vaalit.fi/en/voting-on-election-day</t>
+  </si>
+  <si>
+    <t>Finnish</t>
+  </si>
+  <si>
+    <t>https://vaalit.fi/aanestaminen-vaalipaivana</t>
+  </si>
+  <si>
+    <t>Swedish</t>
+  </si>
+  <si>
+    <t>https://vaalit.fi/sv/rostning-pa-valdagen4</t>
+  </si>
+  <si>
+    <t>Northern Sami</t>
+  </si>
+  <si>
+    <t>https://vaalit.fi/se/ravvagat-jienasteapmai</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>viw-08B505A48A2CEF3474D7ECD6140D9999</t>
+  </si>
+  <si>
+    <t>Hindi</t>
+  </si>
+  <si>
+    <t>https://www.eci.gov.in/faq/hi/how-to-vote/</t>
+  </si>
+  <si>
+    <t>https://ecisveep.nic.in/voters/how-to-vote/</t>
+  </si>
+  <si>
+    <t>Ireland</t>
+  </si>
+  <si>
+    <t>viw-08E38E35B84EAD54307A3177C864948B</t>
+  </si>
+  <si>
+    <t>https://www.electoralcommission.ie/what-you-need-to-vote/</t>
+  </si>
+  <si>
+    <t>Irish</t>
+  </si>
+  <si>
+    <t>https://www.electoralcommission.ie/ga/ceard-a-theastaionn-chun-vota-a-chaitheamh/</t>
+  </si>
+  <si>
+    <t>viw-08E5771E4C081FD1FA6D6E47D78E6D73</t>
+  </si>
+  <si>
+    <t>https://electoralsearch.eci.gov.in/</t>
+  </si>
+  <si>
+    <t>Angola</t>
+  </si>
+  <si>
+    <t>viw-097A29C507FFACD31DB44CFFC0099D19</t>
+  </si>
+  <si>
+    <t>https://www.cne.ao/</t>
+  </si>
+  <si>
+    <t>Malaysia</t>
+  </si>
+  <si>
+    <t>viw-09C391615C41ADFE6A23ED9E8FED839D</t>
+  </si>
+  <si>
+    <t>Bahasa Melayu</t>
+  </si>
+  <si>
+    <t>https://spr.gov.my/pendaftaran-pemilih/</t>
+  </si>
+  <si>
+    <t>viw-0A265493E1471F7AB376DCC3F3246B37</t>
+  </si>
+  <si>
+    <t>https://www.eci.gov.in/faq/hi/how-to-register/</t>
+  </si>
+  <si>
+    <t>https://www.eci.gov.in/faq/en/how-to-register/</t>
+  </si>
+  <si>
+    <t>Hong Kong</t>
+  </si>
+  <si>
+    <t>viw-0A4D46B4BC6F596B3824C49ADAF759F1</t>
+  </si>
+  <si>
+    <t>voter-registration-online</t>
+  </si>
+  <si>
+    <t>https://eform.cefs.gov.hk/form/vre001/en/</t>
+  </si>
+  <si>
+    <t>Traditional Chinese</t>
+  </si>
+  <si>
+    <t>https://eform.cefs.gov.hk/form/vre001/tc/</t>
+  </si>
+  <si>
+    <t>Simplified Chinese</t>
+  </si>
+  <si>
+    <t>https://eform.cefs.gov.hk/form/vre001/sc/</t>
+  </si>
+  <si>
+    <t>Trinidad And Tobago</t>
+  </si>
+  <si>
+    <t>viw-0A84424D89DA17EC689C5B5883B8E608</t>
+  </si>
+  <si>
+    <t>https://ebctt.com/electoral-process/polling-day-activities/</t>
+  </si>
+  <si>
+    <t>Lesotho</t>
+  </si>
+  <si>
+    <t>viw-0A849CED316C0BD290CCFED830099886</t>
+  </si>
+  <si>
+    <t>https://iec.org.ls/voting/</t>
+  </si>
+  <si>
+    <t>Bulgaria</t>
+  </si>
+  <si>
+    <t>viw-0A8D828481142D18F9FBC6886634787F</t>
+  </si>
+  <si>
+    <t>Bulgarian</t>
+  </si>
+  <si>
+    <t>https://www.cik.bg/bg/ns19.04.2026/ukazi</t>
+  </si>
+  <si>
+    <t>Philippines</t>
+  </si>
+  <si>
+    <t>viw-0A985B1DEE67168D50D7F2B6094EED86</t>
+  </si>
+  <si>
+    <t>https://comelec.gov.ph/?r=VoterRegistration/Resolutions/res10963</t>
+  </si>
+  <si>
+    <t>viw-0B0CD10CA2FA77ABC402E59CD8CB94D0</t>
+  </si>
+  <si>
+    <t>https://ec.gov.gh/registration/</t>
+  </si>
+  <si>
+    <t>viw-0B37EA6917CA03440105D921FD5D7F8A</t>
+  </si>
+  <si>
+    <t>https://www.vrk.lt/en/rinkimai</t>
+  </si>
+  <si>
+    <t>https://www.vrk.lt/rinkimai</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>viw-0B9DED619C77547F718262D6C1A8BA3A</t>
+  </si>
+  <si>
+    <t>https://www.juntaelectoralcentral.es/cs/jec/informacion#Voto%20por%20correspondencia</t>
+  </si>
+  <si>
+    <t>Sri Lanka</t>
+  </si>
+  <si>
+    <t>viw-0BB148A033AF644624814B6616B19770</t>
+  </si>
+  <si>
+    <t>https://elections.gov.lk/en/elections/elections_postal_voting_E.html</t>
+  </si>
+  <si>
+    <t>Sinhala</t>
+  </si>
+  <si>
+    <t>https://elections.gov.lk/si/elections/elections_postal_voting_S.html</t>
+  </si>
+  <si>
+    <t>Tamil</t>
+  </si>
+  <si>
+    <t>https://elections.gov.lk/ta/elections/elections_postal_voting_T.html</t>
+  </si>
+  <si>
+    <t>viw-0BF027ED5D75CDD386A2826A71875146</t>
+  </si>
+  <si>
+    <t>https://www.eld.gov.sg/voters_dosdonts.html</t>
+  </si>
+  <si>
+    <t>Sierra Leone</t>
+  </si>
+  <si>
+    <t>viw-0C2A59C4B9EEA0A8F6FB75F279234E0E</t>
+  </si>
+  <si>
+    <t>voter-id-registration-requirements</t>
+  </si>
+  <si>
+    <t>https://ec.gov.sl/voter-registration/</t>
+  </si>
+  <si>
+    <t>El Salvador</t>
+  </si>
+  <si>
+    <t>viw-0CBA4D3D6299705EC2AA7254AC2E7DEA</t>
+  </si>
+  <si>
+    <t>https://www.tse.gob.sv/publico/inicio</t>
+  </si>
+  <si>
+    <t>viw-0CBDE6567759E0F964771F5F81DC9BC4</t>
+  </si>
+  <si>
+    <t>viw-0CF074AE2A27A60A3865EBA7CE071445</t>
+  </si>
+  <si>
+    <t>https://www.elections.ca/content.aspx?section=vot&amp;dir=vote&amp;document=index&amp;lang=e#mail</t>
   </si>
 </sst>
 </file>
@@ -929,17 +926,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F9011C2-C592-46F0-A19C-A926B96F488E}">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.88671875" customWidth="1"/>
     <col min="3" max="3" width="48.5546875" customWidth="1"/>
     <col min="4" max="4" width="32.6640625" customWidth="1"/>
-    <col min="5" max="5" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.21875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="80" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="12.44140625" customWidth="1"/>
-    <col min="9" max="9" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -973,611 +970,611 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" t="s">
         <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H3" t="s">
         <v>16</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H4" t="s">
         <v>16</v>
       </c>
       <c r="I4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="G5" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s">
         <v>16</v>
       </c>
       <c r="I5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="G6" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H6" t="s">
         <v>16</v>
       </c>
       <c r="I6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="G7" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H7" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="G8" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H8" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F9" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="G9" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H9" t="s">
         <v>16</v>
       </c>
       <c r="I9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="E10" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="F10" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="G10" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
       </c>
       <c r="I10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="D11" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E11" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="F11" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="G11" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
       </c>
       <c r="I11" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E12" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="F12" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="G12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
       </c>
       <c r="I12" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="D13" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="E13" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="G13" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
       </c>
       <c r="I13" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="E14" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="G14" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H14" t="s">
         <v>16</v>
       </c>
       <c r="I14" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" t="s">
         <v>10</v>
       </c>
-      <c r="C15" t="s">
-        <v>57</v>
-      </c>
-      <c r="D15" t="s">
-        <v>58</v>
-      </c>
       <c r="E15" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="G15" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H15" t="s">
         <v>16</v>
       </c>
       <c r="I15" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" t="s">
         <v>10</v>
       </c>
-      <c r="C16" t="s">
-        <v>63</v>
-      </c>
-      <c r="D16" t="s">
-        <v>64</v>
-      </c>
       <c r="E16" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="F16" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="G16" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H16" t="s">
         <v>16</v>
       </c>
       <c r="I16" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="D17" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="E17" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F17" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="G17" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H17" t="s">
         <v>16</v>
       </c>
       <c r="I17" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="D18" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="E18" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F18" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="G18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H18" t="s">
         <v>16</v>
       </c>
       <c r="I18" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E19" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="F19" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G19" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H19" t="s">
         <v>16</v>
       </c>
       <c r="I19" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>9</v>
+        <v>89</v>
       </c>
       <c r="B20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="E20" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F20" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H20" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I20" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D21" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="E21" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="F21" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="G21" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H21" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I21" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D22" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" t="s">
+        <v>94</v>
+      </c>
+      <c r="F22" t="s">
+        <v>95</v>
+      </c>
+      <c r="G22" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" t="s">
         <v>12</v>
       </c>
-      <c r="E22" t="s">
-        <v>87</v>
-      </c>
-      <c r="F22" t="s">
-        <v>88</v>
-      </c>
-      <c r="G22" t="s">
-        <v>22</v>
-      </c>
-      <c r="H22" t="s">
-        <v>16</v>
-      </c>
       <c r="I22" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
@@ -1585,405 +1582,405 @@
         <v>89</v>
       </c>
       <c r="B23" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C23" t="s">
         <v>90</v>
       </c>
       <c r="D23" t="s">
-        <v>91</v>
+        <v>32</v>
       </c>
       <c r="E23" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="F23" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G23" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H23" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I23" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B24" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C24" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D24" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="E24" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="F24" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G24" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H24" t="s">
         <v>16</v>
       </c>
       <c r="I24" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C25" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D25" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E25" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F25" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G25" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H25" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I25" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B26" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C26" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D26" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E26" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F26" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G26" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H26" t="s">
         <v>16</v>
       </c>
       <c r="I26" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B27" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D27" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E27" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F27" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G27" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H27" t="s">
         <v>16</v>
       </c>
       <c r="I27" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B28" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C28" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D28" t="s">
-        <v>106</v>
+        <v>39</v>
       </c>
       <c r="E28" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G28" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H28" t="s">
         <v>16</v>
       </c>
       <c r="I28" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B29" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C29" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D29" t="s">
-        <v>106</v>
+        <v>42</v>
       </c>
       <c r="E29" t="s">
-        <v>108</v>
+        <v>24</v>
       </c>
       <c r="F29" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G29" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H29" t="s">
         <v>16</v>
       </c>
       <c r="I29" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" t="s">
+        <v>114</v>
+      </c>
+      <c r="D30" t="s">
         <v>10</v>
       </c>
-      <c r="C30" t="s">
-        <v>111</v>
-      </c>
-      <c r="D30" t="s">
-        <v>112</v>
-      </c>
       <c r="E30" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F30" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G30" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H30" t="s">
         <v>16</v>
       </c>
       <c r="I30" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="B31" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" t="s">
+        <v>117</v>
+      </c>
+      <c r="D31" t="s">
         <v>10</v>
       </c>
-      <c r="C31" t="s">
-        <v>116</v>
-      </c>
-      <c r="D31" t="s">
-        <v>19</v>
-      </c>
       <c r="E31" t="s">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F31" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G31" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H31" t="s">
         <v>16</v>
       </c>
       <c r="I31" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="B32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" t="s">
+        <v>117</v>
+      </c>
+      <c r="D32" t="s">
         <v>10</v>
       </c>
-      <c r="C32" t="s">
-        <v>118</v>
-      </c>
-      <c r="D32" t="s">
-        <v>112</v>
-      </c>
       <c r="E32" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F32" t="s">
         <v>119</v>
       </c>
       <c r="G32" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H32" t="s">
         <v>16</v>
       </c>
       <c r="I32" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="B33" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C33" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D33" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="E33" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F33" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G33" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H33" t="s">
         <v>16</v>
       </c>
       <c r="I33" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="B34" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D34" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="E34" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="F34" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G34" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H34" t="s">
         <v>16</v>
       </c>
       <c r="I34" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B35" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C35" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D35" t="s">
-        <v>33</v>
+        <v>122</v>
       </c>
       <c r="E35" t="s">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="F35" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G35" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H35" t="s">
         <v>16</v>
       </c>
       <c r="I35" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C36" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D36" t="s">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="E36" t="s">
-        <v>129</v>
+        <v>15</v>
       </c>
       <c r="F36" t="s">
         <v>130</v>
       </c>
       <c r="G36" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H36" t="s">
         <v>16</v>
       </c>
       <c r="I36" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
@@ -1991,28 +1988,28 @@
         <v>131</v>
       </c>
       <c r="B37" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C37" t="s">
         <v>132</v>
       </c>
       <c r="D37" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="E37" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F37" t="s">
         <v>133</v>
       </c>
       <c r="G37" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H37" t="s">
         <v>16</v>
       </c>
       <c r="I37" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
@@ -2020,28 +2017,28 @@
         <v>134</v>
       </c>
       <c r="B38" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C38" t="s">
         <v>135</v>
       </c>
       <c r="D38" t="s">
+        <v>14</v>
+      </c>
+      <c r="E38" t="s">
         <v>136</v>
-      </c>
-      <c r="E38" t="s">
-        <v>20</v>
       </c>
       <c r="F38" t="s">
         <v>137</v>
       </c>
       <c r="G38" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H38" t="s">
         <v>16</v>
       </c>
       <c r="I38" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
@@ -2049,347 +2046,376 @@
         <v>138</v>
       </c>
       <c r="B39" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C39" t="s">
         <v>139</v>
       </c>
       <c r="D39" t="s">
+        <v>44</v>
+      </c>
+      <c r="E39" t="s">
+        <v>15</v>
+      </c>
+      <c r="F39" t="s">
         <v>140</v>
       </c>
-      <c r="E39" t="s">
-        <v>20</v>
-      </c>
-      <c r="F39" t="s">
-        <v>141</v>
-      </c>
       <c r="G39" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H39" t="s">
         <v>16</v>
       </c>
       <c r="I39" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>31</v>
+      </c>
+      <c r="B40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" t="s">
+        <v>141</v>
+      </c>
+      <c r="D40" t="s">
+        <v>33</v>
+      </c>
+      <c r="E40" t="s">
+        <v>15</v>
+      </c>
+      <c r="F40" t="s">
         <v>142</v>
       </c>
-      <c r="B40" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" t="s">
-        <v>143</v>
-      </c>
-      <c r="D40" t="s">
-        <v>144</v>
-      </c>
-      <c r="E40" t="s">
-        <v>20</v>
-      </c>
-      <c r="F40" t="s">
-        <v>145</v>
-      </c>
       <c r="G40" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H40" t="s">
         <v>16</v>
       </c>
       <c r="I40" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>142</v>
+        <v>18</v>
       </c>
       <c r="B41" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C41" t="s">
         <v>143</v>
       </c>
       <c r="D41" t="s">
+        <v>25</v>
+      </c>
+      <c r="E41" t="s">
+        <v>15</v>
+      </c>
+      <c r="F41" t="s">
         <v>144</v>
       </c>
-      <c r="E41" t="s">
-        <v>65</v>
-      </c>
-      <c r="F41" t="s">
-        <v>146</v>
-      </c>
       <c r="G41" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H41" t="s">
         <v>16</v>
       </c>
       <c r="I41" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="B42" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C42" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D42" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E42" t="s">
         <v>20</v>
       </c>
       <c r="F42" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G42" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H42" t="s">
         <v>16</v>
       </c>
       <c r="I42" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>67</v>
+        <v>146</v>
       </c>
       <c r="B43" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C43" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D43" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E43" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F43" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G43" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H43" t="s">
         <v>16</v>
       </c>
       <c r="I43" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>149</v>
+      </c>
+      <c r="B44" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" t="s">
+        <v>150</v>
+      </c>
+      <c r="D44" t="s">
+        <v>37</v>
+      </c>
+      <c r="E44" t="s">
+        <v>15</v>
+      </c>
+      <c r="F44" t="s">
         <v>151</v>
       </c>
-      <c r="B44" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" t="s">
-        <v>152</v>
-      </c>
-      <c r="D44" t="s">
-        <v>58</v>
-      </c>
-      <c r="E44" t="s">
-        <v>129</v>
-      </c>
-      <c r="F44" t="s">
-        <v>153</v>
-      </c>
       <c r="G44" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H44" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I44" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B45" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C45" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D45" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E45" t="s">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="F45" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G45" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H45" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I45" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>149</v>
+      </c>
+      <c r="B46" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" t="s">
+        <v>150</v>
+      </c>
+      <c r="D46" t="s">
+        <v>37</v>
+      </c>
+      <c r="E46" t="s">
         <v>154</v>
       </c>
-      <c r="B46" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" t="s">
+      <c r="F46" t="s">
         <v>155</v>
       </c>
-      <c r="D46" t="s">
-        <v>33</v>
-      </c>
-      <c r="E46" t="s">
-        <v>157</v>
-      </c>
-      <c r="F46" t="s">
-        <v>158</v>
-      </c>
       <c r="G46" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H46" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I46" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>134</v>
+        <v>71</v>
       </c>
       <c r="B47" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C47" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D47" t="s">
         <v>19</v>
       </c>
       <c r="E47" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F47" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G47" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H47" t="s">
         <v>16</v>
       </c>
       <c r="I47" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>158</v>
+      </c>
+      <c r="B48" t="s">
+        <v>9</v>
+      </c>
+      <c r="C48" t="s">
+        <v>159</v>
+      </c>
+      <c r="D48" t="s">
+        <v>160</v>
+      </c>
+      <c r="E48" t="s">
+        <v>15</v>
+      </c>
+      <c r="F48" t="s">
         <v>161</v>
       </c>
-      <c r="B48" t="s">
-        <v>10</v>
-      </c>
-      <c r="C48" t="s">
-        <v>162</v>
-      </c>
-      <c r="D48" t="s">
-        <v>163</v>
-      </c>
-      <c r="E48" t="s">
-        <v>13</v>
-      </c>
-      <c r="F48" t="s">
-        <v>164</v>
-      </c>
       <c r="G48" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H48" t="s">
         <v>16</v>
       </c>
       <c r="I48" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B49" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C49" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D49" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E49" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F49" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G49" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H49" t="s">
         <v>16</v>
       </c>
       <c r="I49" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>35</v>
+      </c>
+      <c r="B50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C50" t="s">
         <v>165</v>
       </c>
-      <c r="B50" t="s">
-        <v>10</v>
-      </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
+        <v>38</v>
+      </c>
+      <c r="E50" t="s">
+        <v>15</v>
+      </c>
+      <c r="F50" t="s">
+        <v>43</v>
+      </c>
+      <c r="G50" t="s">
+        <v>16</v>
+      </c>
+      <c r="H50" t="s">
+        <v>16</v>
+      </c>
+      <c r="I50" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>41</v>
+      </c>
+      <c r="B51" t="s">
+        <v>9</v>
+      </c>
+      <c r="C51" t="s">
         <v>166</v>
       </c>
-      <c r="D50" t="s">
-        <v>33</v>
-      </c>
-      <c r="E50" t="s">
-        <v>168</v>
-      </c>
-      <c r="F50" t="s">
-        <v>169</v>
-      </c>
-      <c r="G50" t="s">
-        <v>22</v>
-      </c>
-      <c r="H50" t="s">
-        <v>16</v>
-      </c>
-      <c r="I50" t="s">
-        <v>16</v>
+      <c r="D51" t="s">
+        <v>37</v>
+      </c>
+      <c r="E51" t="s">
+        <v>15</v>
+      </c>
+      <c r="F51" t="s">
+        <v>167</v>
+      </c>
+      <c r="G51" t="s">
+        <v>16</v>
+      </c>
+      <c r="H51" t="s">
+        <v>16</v>
+      </c>
+      <c r="I51" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/input.xlsx
+++ b/input.xlsx
@@ -5855,7 +5855,7 @@
     <t>viw-A5A8754D1BBF67116E5E3C7E887A538B</t>
   </si>
   <si>
-    <t>https://www.interieur.gouv.fr/actualites/actualites-du-ministere/elections-legislatives-2024</t>
+    <t>https://www.vie-publique.fr/en-bref/303896-election-presidentielle-2027-les-dates-sont-connues</t>
   </si>
   <si>
     <t>viw-A62C9E9DBDCF8776C5B82E261738979E</t>
@@ -12177,7 +12177,7 @@
         <v>205</v>
       </c>
       <c r="G66" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H66" s="0" t="s">
         <v>16</v>
@@ -12293,7 +12293,7 @@
         <v>216</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H70" s="0" t="s">
         <v>16</v>
@@ -12322,7 +12322,7 @@
         <v>217</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H71" s="0" t="s">
         <v>16</v>
@@ -12670,7 +12670,7 @@
         <v>241</v>
       </c>
       <c r="G83" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H83" s="0" t="s">
         <v>16</v>
@@ -12699,7 +12699,7 @@
         <v>243</v>
       </c>
       <c r="G84" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H84" s="0" t="s">
         <v>16</v>
@@ -12728,7 +12728,7 @@
         <v>245</v>
       </c>
       <c r="G85" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H85" s="0" t="s">
         <v>16</v>
@@ -12757,7 +12757,7 @@
         <v>247</v>
       </c>
       <c r="G86" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H86" s="0" t="s">
         <v>16</v>
@@ -12786,7 +12786,7 @@
         <v>251</v>
       </c>
       <c r="G87" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H87" s="0" t="s">
         <v>16</v>
@@ -12960,7 +12960,7 @@
         <v>266</v>
       </c>
       <c r="G93" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H93" s="0" t="s">
         <v>16</v>
@@ -12989,7 +12989,7 @@
         <v>268</v>
       </c>
       <c r="G94" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H94" s="0" t="s">
         <v>16</v>
@@ -13018,7 +13018,7 @@
         <v>269</v>
       </c>
       <c r="G95" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H95" s="0" t="s">
         <v>16</v>
@@ -13511,7 +13511,7 @@
         <v>314</v>
       </c>
       <c r="G112" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H112" s="0" t="s">
         <v>16</v>
@@ -13801,7 +13801,7 @@
         <v>335</v>
       </c>
       <c r="G122" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H122" s="0" t="s">
         <v>16</v>
@@ -13830,7 +13830,7 @@
         <v>336</v>
       </c>
       <c r="G123" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H123" s="0" t="s">
         <v>16</v>
@@ -14062,7 +14062,7 @@
         <v>358</v>
       </c>
       <c r="G131" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H131" s="0" t="s">
         <v>16</v>
@@ -14323,7 +14323,7 @@
         <v>383</v>
       </c>
       <c r="G140" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H140" s="0" t="s">
         <v>16</v>
@@ -14381,7 +14381,7 @@
         <v>358</v>
       </c>
       <c r="G142" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H142" s="0" t="s">
         <v>16</v>
@@ -14729,7 +14729,7 @@
         <v>413</v>
       </c>
       <c r="G154" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H154" s="0" t="s">
         <v>16</v>
@@ -14758,7 +14758,7 @@
         <v>414</v>
       </c>
       <c r="G155" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H155" s="0" t="s">
         <v>16</v>
@@ -14816,7 +14816,7 @@
         <v>419</v>
       </c>
       <c r="G157" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H157" s="0" t="s">
         <v>16</v>
@@ -14845,7 +14845,7 @@
         <v>419</v>
       </c>
       <c r="G158" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H158" s="0" t="s">
         <v>16</v>
@@ -14932,7 +14932,7 @@
         <v>427</v>
       </c>
       <c r="G161" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H161" s="0" t="s">
         <v>16</v>
@@ -14961,7 +14961,7 @@
         <v>429</v>
       </c>
       <c r="G162" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H162" s="0" t="s">
         <v>16</v>
@@ -15251,7 +15251,7 @@
         <v>445</v>
       </c>
       <c r="G172" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H172" s="0" t="s">
         <v>16</v>
@@ -15744,7 +15744,7 @@
         <v>477</v>
       </c>
       <c r="G189" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H189" s="0" t="s">
         <v>16</v>
@@ -15860,7 +15860,7 @@
         <v>484</v>
       </c>
       <c r="G193" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H193" s="0" t="s">
         <v>16</v>
@@ -15889,7 +15889,7 @@
         <v>484</v>
       </c>
       <c r="G194" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H194" s="0" t="s">
         <v>16</v>
@@ -16150,7 +16150,7 @@
         <v>499</v>
       </c>
       <c r="G203" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H203" s="0" t="s">
         <v>16</v>
@@ -16208,7 +16208,7 @@
         <v>503</v>
       </c>
       <c r="G205" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H205" s="0" t="s">
         <v>16</v>
@@ -16411,7 +16411,7 @@
         <v>513</v>
       </c>
       <c r="G212" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H212" s="0" t="s">
         <v>16</v>
@@ -16440,7 +16440,7 @@
         <v>514</v>
       </c>
       <c r="G213" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H213" s="0" t="s">
         <v>16</v>
@@ -16730,7 +16730,7 @@
         <v>533</v>
       </c>
       <c r="G223" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H223" s="0" t="s">
         <v>16</v>
@@ -16817,7 +16817,7 @@
         <v>540</v>
       </c>
       <c r="G226" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H226" s="0" t="s">
         <v>16</v>
@@ -16846,7 +16846,7 @@
         <v>540</v>
       </c>
       <c r="G227" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H227" s="0" t="s">
         <v>16</v>
@@ -16933,7 +16933,7 @@
         <v>545</v>
       </c>
       <c r="G230" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H230" s="0" t="s">
         <v>16</v>
@@ -16962,7 +16962,7 @@
         <v>547</v>
       </c>
       <c r="G231" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H231" s="0" t="s">
         <v>16</v>
@@ -17194,7 +17194,7 @@
         <v>563</v>
       </c>
       <c r="G239" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H239" s="0" t="s">
         <v>16</v>
@@ -17223,7 +17223,7 @@
         <v>564</v>
       </c>
       <c r="G240" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H240" s="0" t="s">
         <v>16</v>
@@ -17252,7 +17252,7 @@
         <v>567</v>
       </c>
       <c r="G241" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H241" s="0" t="s">
         <v>16</v>
@@ -17281,7 +17281,7 @@
         <v>570</v>
       </c>
       <c r="G242" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H242" s="0" t="s">
         <v>16</v>
@@ -17310,7 +17310,7 @@
         <v>572</v>
       </c>
       <c r="G243" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H243" s="0" t="s">
         <v>16</v>
@@ -17339,7 +17339,7 @@
         <v>573</v>
       </c>
       <c r="G244" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H244" s="0" t="s">
         <v>16</v>
@@ -17455,7 +17455,7 @@
         <v>580</v>
       </c>
       <c r="G248" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H248" s="0" t="s">
         <v>16</v>
@@ -17571,7 +17571,7 @@
         <v>588</v>
       </c>
       <c r="G252" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H252" s="0" t="s">
         <v>16</v>
@@ -17745,7 +17745,7 @@
         <v>598</v>
       </c>
       <c r="G258" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H258" s="0" t="s">
         <v>16</v>
@@ -17861,7 +17861,7 @@
         <v>606</v>
       </c>
       <c r="G262" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H262" s="0" t="s">
         <v>16</v>
@@ -17948,7 +17948,7 @@
         <v>612</v>
       </c>
       <c r="G265" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H265" s="0" t="s">
         <v>16</v>
@@ -17977,7 +17977,7 @@
         <v>613</v>
       </c>
       <c r="G266" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H266" s="0" t="s">
         <v>16</v>
@@ -18006,7 +18006,7 @@
         <v>614</v>
       </c>
       <c r="G267" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H267" s="0" t="s">
         <v>16</v>
@@ -18035,7 +18035,7 @@
         <v>314</v>
       </c>
       <c r="G268" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H268" s="0" t="s">
         <v>16</v>
@@ -18209,7 +18209,7 @@
         <v>358</v>
       </c>
       <c r="G274" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H274" s="0" t="s">
         <v>16</v>
@@ -18615,7 +18615,7 @@
         <v>648</v>
       </c>
       <c r="G288" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H288" s="0" t="s">
         <v>16</v>
@@ -18876,7 +18876,7 @@
         <v>665</v>
       </c>
       <c r="G297" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H297" s="0" t="s">
         <v>16</v>
@@ -18905,7 +18905,7 @@
         <v>666</v>
       </c>
       <c r="G298" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H298" s="0" t="s">
         <v>16</v>
@@ -19021,7 +19021,7 @@
         <v>484</v>
       </c>
       <c r="G302" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H302" s="0" t="s">
         <v>16</v>
@@ -19050,7 +19050,7 @@
         <v>484</v>
       </c>
       <c r="G303" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H303" s="0" t="s">
         <v>16</v>
@@ -19282,7 +19282,7 @@
         <v>690</v>
       </c>
       <c r="G311" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H311" s="0" t="s">
         <v>16</v>
@@ -19369,7 +19369,7 @@
         <v>695</v>
       </c>
       <c r="G314" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H314" s="0" t="s">
         <v>16</v>
@@ -19456,7 +19456,7 @@
         <v>700</v>
       </c>
       <c r="G317" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H317" s="0" t="s">
         <v>16</v>
@@ -19601,7 +19601,7 @@
         <v>703</v>
       </c>
       <c r="G322" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H322" s="0" t="s">
         <v>16</v>
@@ -19630,7 +19630,7 @@
         <v>707</v>
       </c>
       <c r="G323" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H323" s="0" t="s">
         <v>16</v>
@@ -19688,7 +19688,7 @@
         <v>711</v>
       </c>
       <c r="G325" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H325" s="0" t="s">
         <v>16</v>
@@ -19717,7 +19717,7 @@
         <v>711</v>
       </c>
       <c r="G326" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H326" s="0" t="s">
         <v>16</v>
@@ -19833,7 +19833,7 @@
         <v>416</v>
       </c>
       <c r="G330" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H330" s="0" t="s">
         <v>16</v>
@@ -19978,7 +19978,7 @@
         <v>201</v>
       </c>
       <c r="G335" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H335" s="0" t="s">
         <v>16</v>
@@ -20007,7 +20007,7 @@
         <v>202</v>
       </c>
       <c r="G336" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H336" s="0" t="s">
         <v>16</v>
@@ -20442,7 +20442,7 @@
         <v>748</v>
       </c>
       <c r="G351" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H351" s="0" t="s">
         <v>16</v>
@@ -20703,7 +20703,7 @@
         <v>765</v>
       </c>
       <c r="G360" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H360" s="0" t="s">
         <v>16</v>
@@ -20732,7 +20732,7 @@
         <v>767</v>
       </c>
       <c r="G361" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H361" s="0" t="s">
         <v>16</v>
@@ -20906,7 +20906,7 @@
         <v>779</v>
       </c>
       <c r="G367" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H367" s="0" t="s">
         <v>16</v>
@@ -20993,7 +20993,7 @@
         <v>784</v>
       </c>
       <c r="G370" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H370" s="0" t="s">
         <v>16</v>
@@ -21051,7 +21051,7 @@
         <v>788</v>
       </c>
       <c r="G372" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H372" s="0" t="s">
         <v>16</v>
@@ -21225,7 +21225,7 @@
         <v>796</v>
       </c>
       <c r="G378" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H378" s="0" t="s">
         <v>16</v>
@@ -21428,7 +21428,7 @@
         <v>806</v>
       </c>
       <c r="G385" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H385" s="0" t="s">
         <v>16</v>
@@ -21689,7 +21689,7 @@
         <v>822</v>
       </c>
       <c r="G394" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H394" s="0" t="s">
         <v>16</v>
@@ -21776,7 +21776,7 @@
         <v>567</v>
       </c>
       <c r="G397" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H397" s="0" t="s">
         <v>16</v>
@@ -22472,7 +22472,7 @@
         <v>533</v>
       </c>
       <c r="G421" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H421" s="0" t="s">
         <v>16</v>
@@ -23052,7 +23052,7 @@
         <v>900</v>
       </c>
       <c r="G441" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H441" s="0" t="s">
         <v>16</v>
@@ -23284,7 +23284,7 @@
         <v>413</v>
       </c>
       <c r="G449" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H449" s="0" t="s">
         <v>16</v>
@@ -23313,7 +23313,7 @@
         <v>414</v>
       </c>
       <c r="G450" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H450" s="0" t="s">
         <v>16</v>
@@ -23342,7 +23342,7 @@
         <v>915</v>
       </c>
       <c r="G451" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H451" s="0" t="s">
         <v>16</v>
@@ -23574,7 +23574,7 @@
         <v>926</v>
       </c>
       <c r="G459" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H459" s="0" t="s">
         <v>16</v>
@@ -23603,7 +23603,7 @@
         <v>928</v>
       </c>
       <c r="G460" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H460" s="0" t="s">
         <v>16</v>
@@ -23632,7 +23632,7 @@
         <v>930</v>
       </c>
       <c r="G461" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H461" s="0" t="s">
         <v>16</v>
@@ -24009,7 +24009,7 @@
         <v>703</v>
       </c>
       <c r="G474" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H474" s="0" t="s">
         <v>16</v>
@@ -24038,7 +24038,7 @@
         <v>949</v>
       </c>
       <c r="G475" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H475" s="0" t="s">
         <v>16</v>
@@ -24676,7 +24676,7 @@
         <v>976</v>
       </c>
       <c r="G497" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H497" s="0" t="s">
         <v>16</v>
@@ -24705,7 +24705,7 @@
         <v>572</v>
       </c>
       <c r="G498" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H498" s="0" t="s">
         <v>16</v>
@@ -24821,7 +24821,7 @@
         <v>251</v>
       </c>
       <c r="G502" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H502" s="0" t="s">
         <v>16</v>
@@ -24908,7 +24908,7 @@
         <v>987</v>
       </c>
       <c r="G505" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H505" s="0" t="s">
         <v>16</v>
@@ -25111,7 +25111,7 @@
         <v>998</v>
       </c>
       <c r="G512" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H512" s="0" t="s">
         <v>16</v>
@@ -25140,7 +25140,7 @@
         <v>1000</v>
       </c>
       <c r="G513" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H513" s="0" t="s">
         <v>16</v>
@@ -25198,7 +25198,7 @@
         <v>1004</v>
       </c>
       <c r="G515" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H515" s="0" t="s">
         <v>16</v>
@@ -25227,7 +25227,7 @@
         <v>976</v>
       </c>
       <c r="G516" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H516" s="0" t="s">
         <v>16</v>
@@ -25633,7 +25633,7 @@
         <v>567</v>
       </c>
       <c r="G530" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H530" s="0" t="s">
         <v>16</v>
@@ -25894,7 +25894,7 @@
         <v>588</v>
       </c>
       <c r="G539" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H539" s="0" t="s">
         <v>16</v>
@@ -25981,7 +25981,7 @@
         <v>1044</v>
       </c>
       <c r="G542" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H542" s="0" t="s">
         <v>16</v>
@@ -26010,7 +26010,7 @@
         <v>1045</v>
       </c>
       <c r="G543" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H543" s="0" t="s">
         <v>16</v>
@@ -26126,7 +26126,7 @@
         <v>1053</v>
       </c>
       <c r="G547" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H547" s="0" t="s">
         <v>16</v>
@@ -26155,7 +26155,7 @@
         <v>1055</v>
       </c>
       <c r="G548" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H548" s="0" t="s">
         <v>16</v>
@@ -26184,7 +26184,7 @@
         <v>1056</v>
       </c>
       <c r="G549" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H549" s="0" t="s">
         <v>16</v>
@@ -26271,7 +26271,7 @@
         <v>1062</v>
       </c>
       <c r="G552" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H552" s="0" t="s">
         <v>16</v>
@@ -26358,7 +26358,7 @@
         <v>1067</v>
       </c>
       <c r="G555" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H555" s="0" t="s">
         <v>16</v>
@@ -26387,7 +26387,7 @@
         <v>1069</v>
       </c>
       <c r="G556" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H556" s="0" t="s">
         <v>16</v>
@@ -26445,7 +26445,7 @@
         <v>1073</v>
       </c>
       <c r="G558" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H558" s="0" t="s">
         <v>16</v>
@@ -26474,7 +26474,7 @@
         <v>1075</v>
       </c>
       <c r="G559" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H559" s="0" t="s">
         <v>16</v>
@@ -27228,7 +27228,7 @@
         <v>262</v>
       </c>
       <c r="G585" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H585" s="0" t="s">
         <v>16</v>
@@ -27605,7 +27605,7 @@
         <v>1135</v>
       </c>
       <c r="G598" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H598" s="0" t="s">
         <v>16</v>
@@ -27692,7 +27692,7 @@
         <v>1140</v>
       </c>
       <c r="G601" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H601" s="0" t="s">
         <v>16</v>
@@ -28185,7 +28185,7 @@
         <v>1164</v>
       </c>
       <c r="G618" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H618" s="0" t="s">
         <v>16</v>
@@ -28417,7 +28417,7 @@
         <v>1175</v>
       </c>
       <c r="G626" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H626" s="0" t="s">
         <v>16</v>
@@ -28504,7 +28504,7 @@
         <v>1181</v>
       </c>
       <c r="G629" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H629" s="0" t="s">
         <v>16</v>
@@ -28794,7 +28794,7 @@
         <v>1194</v>
       </c>
       <c r="G639" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H639" s="0" t="s">
         <v>16</v>
@@ -29026,7 +29026,7 @@
         <v>1205</v>
       </c>
       <c r="G647" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H647" s="0" t="s">
         <v>16</v>
@@ -29287,7 +29287,7 @@
         <v>1217</v>
       </c>
       <c r="G656" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H656" s="0" t="s">
         <v>16</v>
@@ -29345,7 +29345,7 @@
         <v>1221</v>
       </c>
       <c r="G658" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H658" s="0" t="s">
         <v>16</v>
@@ -29432,7 +29432,7 @@
         <v>1226</v>
       </c>
       <c r="G661" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H661" s="0" t="s">
         <v>16</v>
@@ -29490,7 +29490,7 @@
         <v>1230</v>
       </c>
       <c r="G663" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H663" s="0" t="s">
         <v>16</v>
@@ -30012,7 +30012,7 @@
         <v>1252</v>
       </c>
       <c r="G681" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H681" s="0" t="s">
         <v>16</v>
@@ -30389,7 +30389,7 @@
         <v>1264</v>
       </c>
       <c r="G694" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H694" s="0" t="s">
         <v>16</v>
@@ -30418,7 +30418,7 @@
         <v>1265</v>
       </c>
       <c r="G695" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H695" s="0" t="s">
         <v>16</v>
@@ -30447,7 +30447,7 @@
         <v>915</v>
       </c>
       <c r="G696" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H696" s="0" t="s">
         <v>16</v>
@@ -30534,7 +30534,7 @@
         <v>1272</v>
       </c>
       <c r="G699" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H699" s="0" t="s">
         <v>16</v>
@@ -30563,7 +30563,7 @@
         <v>1273</v>
       </c>
       <c r="G700" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H700" s="0" t="s">
         <v>16</v>
@@ -30650,7 +30650,7 @@
         <v>358</v>
       </c>
       <c r="G703" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H703" s="0" t="s">
         <v>16</v>
@@ -30737,7 +30737,7 @@
         <v>1281</v>
       </c>
       <c r="G706" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H706" s="0" t="s">
         <v>16</v>
@@ -30766,7 +30766,7 @@
         <v>533</v>
       </c>
       <c r="G707" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H707" s="0" t="s">
         <v>16</v>
@@ -30853,7 +30853,7 @@
         <v>419</v>
       </c>
       <c r="G710" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H710" s="0" t="s">
         <v>16</v>
@@ -30882,7 +30882,7 @@
         <v>419</v>
       </c>
       <c r="G711" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H711" s="0" t="s">
         <v>16</v>
@@ -31201,7 +31201,7 @@
         <v>251</v>
       </c>
       <c r="G722" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H722" s="0" t="s">
         <v>16</v>
@@ -31230,7 +31230,7 @@
         <v>1302</v>
       </c>
       <c r="G723" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H723" s="0" t="s">
         <v>16</v>
@@ -31259,7 +31259,7 @@
         <v>1304</v>
       </c>
       <c r="G724" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H724" s="0" t="s">
         <v>16</v>
@@ -31288,7 +31288,7 @@
         <v>915</v>
       </c>
       <c r="G725" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H725" s="0" t="s">
         <v>16</v>
@@ -31636,7 +31636,7 @@
         <v>1323</v>
       </c>
       <c r="G737" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H737" s="0" t="s">
         <v>16</v>
@@ -31955,7 +31955,7 @@
         <v>606</v>
       </c>
       <c r="G748" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H748" s="0" t="s">
         <v>16</v>
@@ -32100,7 +32100,7 @@
         <v>1346</v>
       </c>
       <c r="G753" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H753" s="0" t="s">
         <v>16</v>
@@ -32129,7 +32129,7 @@
         <v>1347</v>
       </c>
       <c r="G754" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H754" s="0" t="s">
         <v>16</v>
@@ -32187,7 +32187,7 @@
         <v>1351</v>
       </c>
       <c r="G756" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H756" s="0" t="s">
         <v>16</v>
@@ -32303,7 +32303,7 @@
         <v>1357</v>
       </c>
       <c r="G760" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H760" s="0" t="s">
         <v>16</v>
@@ -32332,7 +32332,7 @@
         <v>1358</v>
       </c>
       <c r="G761" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H761" s="0" t="s">
         <v>16</v>
@@ -32564,7 +32564,7 @@
         <v>1368</v>
       </c>
       <c r="G769" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H769" s="0" t="s">
         <v>16</v>
@@ -32651,7 +32651,7 @@
         <v>510</v>
       </c>
       <c r="G772" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H772" s="0" t="s">
         <v>16</v>
@@ -32680,7 +32680,7 @@
         <v>511</v>
       </c>
       <c r="G773" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H773" s="0" t="s">
         <v>16</v>
@@ -32912,7 +32912,7 @@
         <v>1383</v>
       </c>
       <c r="G781" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H781" s="0" t="s">
         <v>16</v>
@@ -33463,7 +33463,7 @@
         <v>1413</v>
       </c>
       <c r="G800" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H800" s="0" t="s">
         <v>16</v>
@@ -33492,7 +33492,7 @@
         <v>1415</v>
       </c>
       <c r="G801" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H801" s="0" t="s">
         <v>16</v>
@@ -33521,7 +33521,7 @@
         <v>1416</v>
       </c>
       <c r="G802" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H802" s="0" t="s">
         <v>16</v>
@@ -33869,7 +33869,7 @@
         <v>1332</v>
       </c>
       <c r="G814" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H814" s="0" t="s">
         <v>16</v>
@@ -34043,7 +34043,7 @@
         <v>1441</v>
       </c>
       <c r="G820" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H820" s="0" t="s">
         <v>16</v>
@@ -34072,7 +34072,7 @@
         <v>245</v>
       </c>
       <c r="G821" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H821" s="0" t="s">
         <v>16</v>
@@ -34101,7 +34101,7 @@
         <v>243</v>
       </c>
       <c r="G822" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H822" s="0" t="s">
         <v>16</v>
@@ -34130,7 +34130,7 @@
         <v>241</v>
       </c>
       <c r="G823" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H823" s="0" t="s">
         <v>16</v>
@@ -34333,7 +34333,7 @@
         <v>1448</v>
       </c>
       <c r="G830" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H830" s="0" t="s">
         <v>16</v>
@@ -34478,7 +34478,7 @@
         <v>1455</v>
       </c>
       <c r="G835" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H835" s="0" t="s">
         <v>16</v>
@@ -34507,7 +34507,7 @@
         <v>1456</v>
       </c>
       <c r="G836" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H836" s="0" t="s">
         <v>16</v>
@@ -34681,7 +34681,7 @@
         <v>419</v>
       </c>
       <c r="G842" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H842" s="0" t="s">
         <v>16</v>
@@ -34710,7 +34710,7 @@
         <v>419</v>
       </c>
       <c r="G843" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H843" s="0" t="s">
         <v>16</v>
@@ -34797,7 +34797,7 @@
         <v>1470</v>
       </c>
       <c r="G846" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H846" s="0" t="s">
         <v>16</v>
@@ -34855,7 +34855,7 @@
         <v>784</v>
       </c>
       <c r="G848" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H848" s="0" t="s">
         <v>16</v>
@@ -34971,7 +34971,7 @@
         <v>1481</v>
       </c>
       <c r="G852" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H852" s="0" t="s">
         <v>16</v>
@@ -35000,7 +35000,7 @@
         <v>1483</v>
       </c>
       <c r="G853" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H853" s="0" t="s">
         <v>16</v>
@@ -35319,7 +35319,7 @@
         <v>445</v>
       </c>
       <c r="G864" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H864" s="0" t="s">
         <v>16</v>
@@ -35406,7 +35406,7 @@
         <v>1507</v>
       </c>
       <c r="G867" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H867" s="0" t="s">
         <v>16</v>
@@ -35493,7 +35493,7 @@
         <v>1511</v>
       </c>
       <c r="G870" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H870" s="0" t="s">
         <v>16</v>
@@ -35696,7 +35696,7 @@
         <v>1522</v>
       </c>
       <c r="G877" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H877" s="0" t="s">
         <v>16</v>
@@ -35725,7 +35725,7 @@
         <v>1524</v>
       </c>
       <c r="G878" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H878" s="0" t="s">
         <v>16</v>
@@ -35899,7 +35899,7 @@
         <v>1534</v>
       </c>
       <c r="G884" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H884" s="0" t="s">
         <v>16</v>
@@ -35928,7 +35928,7 @@
         <v>1536</v>
       </c>
       <c r="G885" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H885" s="0" t="s">
         <v>16</v>
@@ -36015,7 +36015,7 @@
         <v>1542</v>
       </c>
       <c r="G888" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H888" s="0" t="s">
         <v>16</v>
@@ -36218,7 +36218,7 @@
         <v>1260</v>
       </c>
       <c r="G895" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H895" s="0" t="s">
         <v>16</v>
@@ -36247,7 +36247,7 @@
         <v>533</v>
       </c>
       <c r="G896" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H896" s="0" t="s">
         <v>16</v>
@@ -36392,7 +36392,7 @@
         <v>441</v>
       </c>
       <c r="G901" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H901" s="0" t="s">
         <v>16</v>
@@ -36421,7 +36421,7 @@
         <v>374</v>
       </c>
       <c r="G902" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H902" s="0" t="s">
         <v>16</v>
@@ -36711,7 +36711,7 @@
         <v>859</v>
       </c>
       <c r="G912" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H912" s="0" t="s">
         <v>16</v>
@@ -36798,7 +36798,7 @@
         <v>1583</v>
       </c>
       <c r="G915" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H915" s="0" t="s">
         <v>16</v>
@@ -36827,7 +36827,7 @@
         <v>1585</v>
       </c>
       <c r="G916" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H916" s="0" t="s">
         <v>16</v>
@@ -36856,7 +36856,7 @@
         <v>374</v>
       </c>
       <c r="G917" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H917" s="0" t="s">
         <v>16</v>
@@ -37030,7 +37030,7 @@
         <v>567</v>
       </c>
       <c r="G923" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H923" s="0" t="s">
         <v>16</v>
@@ -37262,7 +37262,7 @@
         <v>1603</v>
       </c>
       <c r="G931" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H931" s="0" t="s">
         <v>16</v>
@@ -37291,7 +37291,7 @@
         <v>976</v>
       </c>
       <c r="G932" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H932" s="0" t="s">
         <v>16</v>
@@ -37610,7 +37610,7 @@
         <v>606</v>
       </c>
       <c r="G943" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H943" s="0" t="s">
         <v>16</v>
@@ -37958,7 +37958,7 @@
         <v>1641</v>
       </c>
       <c r="G955" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H955" s="0" t="s">
         <v>16</v>
@@ -38132,7 +38132,7 @@
         <v>1651</v>
       </c>
       <c r="G961" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H961" s="0" t="s">
         <v>16</v>
@@ -38161,7 +38161,7 @@
         <v>1652</v>
       </c>
       <c r="G962" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H962" s="0" t="s">
         <v>16</v>
@@ -38190,7 +38190,7 @@
         <v>1534</v>
       </c>
       <c r="G963" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H963" s="0" t="s">
         <v>16</v>
@@ -38364,7 +38364,7 @@
         <v>1661</v>
       </c>
       <c r="G969" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H969" s="0" t="s">
         <v>16</v>
@@ -38422,7 +38422,7 @@
         <v>1664</v>
       </c>
       <c r="G971" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H971" s="0" t="s">
         <v>16</v>
@@ -38480,7 +38480,7 @@
         <v>804</v>
       </c>
       <c r="G973" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H973" s="0" t="s">
         <v>16</v>
@@ -38625,7 +38625,7 @@
         <v>1670</v>
       </c>
       <c r="G978" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H978" s="0" t="s">
         <v>16</v>
@@ -38712,7 +38712,7 @@
         <v>205</v>
       </c>
       <c r="G981" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H981" s="0" t="s">
         <v>16</v>
@@ -38741,7 +38741,7 @@
         <v>1676</v>
       </c>
       <c r="G982" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H982" s="0" t="s">
         <v>16</v>
@@ -38886,7 +38886,7 @@
         <v>1684</v>
       </c>
       <c r="G987" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H987" s="0" t="s">
         <v>16</v>
@@ -38944,7 +38944,7 @@
         <v>1687</v>
       </c>
       <c r="G989" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H989" s="0" t="s">
         <v>16</v>
@@ -39060,7 +39060,7 @@
         <v>1273</v>
       </c>
       <c r="G993" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H993" s="0" t="s">
         <v>16</v>
@@ -39089,7 +39089,7 @@
         <v>765</v>
       </c>
       <c r="G994" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H994" s="0" t="s">
         <v>16</v>
@@ -39147,7 +39147,7 @@
         <v>1698</v>
       </c>
       <c r="G996" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H996" s="0" t="s">
         <v>16</v>
@@ -39176,7 +39176,7 @@
         <v>1700</v>
       </c>
       <c r="G997" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H997" s="0" t="s">
         <v>16</v>
@@ -39408,7 +39408,7 @@
         <v>1712</v>
       </c>
       <c r="G1005" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1005" s="0" t="s">
         <v>16</v>
@@ -39930,7 +39930,7 @@
         <v>1735</v>
       </c>
       <c r="G1023" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1023" s="0" t="s">
         <v>16</v>
@@ -40162,7 +40162,7 @@
         <v>1748</v>
       </c>
       <c r="G1031" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1031" s="0" t="s">
         <v>16</v>
@@ -40191,7 +40191,7 @@
         <v>796</v>
       </c>
       <c r="G1032" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1032" s="0" t="s">
         <v>16</v>
@@ -40249,7 +40249,7 @@
         <v>1753</v>
       </c>
       <c r="G1034" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1034" s="0" t="s">
         <v>16</v>
@@ -40278,7 +40278,7 @@
         <v>1755</v>
       </c>
       <c r="G1035" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1035" s="0" t="s">
         <v>16</v>
@@ -40365,7 +40365,7 @@
         <v>322</v>
       </c>
       <c r="G1038" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1038" s="0" t="s">
         <v>16</v>
@@ -40423,7 +40423,7 @@
         <v>322</v>
       </c>
       <c r="G1040" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1040" s="0" t="s">
         <v>16</v>
@@ -40742,7 +40742,7 @@
         <v>612</v>
       </c>
       <c r="G1051" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1051" s="0" t="s">
         <v>16</v>
@@ -40771,7 +40771,7 @@
         <v>613</v>
       </c>
       <c r="G1052" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1052" s="0" t="s">
         <v>16</v>
@@ -40800,7 +40800,7 @@
         <v>614</v>
       </c>
       <c r="G1053" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1053" s="0" t="s">
         <v>16</v>
@@ -40829,7 +40829,7 @@
         <v>1780</v>
       </c>
       <c r="G1054" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1054" s="0" t="s">
         <v>16</v>
@@ -40858,7 +40858,7 @@
         <v>1782</v>
       </c>
       <c r="G1055" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1055" s="0" t="s">
         <v>16</v>
@@ -41380,7 +41380,7 @@
         <v>1809</v>
       </c>
       <c r="G1073" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1073" s="0" t="s">
         <v>16</v>
@@ -41409,7 +41409,7 @@
         <v>1810</v>
       </c>
       <c r="G1074" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1074" s="0" t="s">
         <v>16</v>
@@ -41438,7 +41438,7 @@
         <v>1811</v>
       </c>
       <c r="G1075" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1075" s="0" t="s">
         <v>16</v>
@@ -41583,7 +41583,7 @@
         <v>606</v>
       </c>
       <c r="G1080" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1080" s="0" t="s">
         <v>16</v>
@@ -41989,7 +41989,7 @@
         <v>765</v>
       </c>
       <c r="G1094" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1094" s="0" t="s">
         <v>16</v>
@@ -42134,7 +42134,7 @@
         <v>1834</v>
       </c>
       <c r="G1099" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1099" s="0" t="s">
         <v>16</v>
@@ -42163,7 +42163,7 @@
         <v>1835</v>
       </c>
       <c r="G1100" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1100" s="0" t="s">
         <v>16</v>
@@ -42337,7 +42337,7 @@
         <v>1846</v>
       </c>
       <c r="G1106" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1106" s="0" t="s">
         <v>16</v>
@@ -42366,7 +42366,7 @@
         <v>1848</v>
       </c>
       <c r="G1107" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1107" s="0" t="s">
         <v>16</v>
@@ -42395,7 +42395,7 @@
         <v>1849</v>
       </c>
       <c r="G1108" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1108" s="0" t="s">
         <v>16</v>
@@ -42685,7 +42685,7 @@
         <v>1865</v>
       </c>
       <c r="G1118" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1118" s="0" t="s">
         <v>16</v>
@@ -42714,7 +42714,7 @@
         <v>1867</v>
       </c>
       <c r="G1119" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1119" s="0" t="s">
         <v>16</v>
@@ -43033,7 +43033,7 @@
         <v>1879</v>
       </c>
       <c r="G1130" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1130" s="0" t="s">
         <v>16</v>
@@ -43062,7 +43062,7 @@
         <v>1879</v>
       </c>
       <c r="G1131" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1131" s="0" t="s">
         <v>16</v>
@@ -43149,7 +43149,7 @@
         <v>1884</v>
       </c>
       <c r="G1134" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1134" s="0" t="s">
         <v>16</v>
@@ -43207,7 +43207,7 @@
         <v>1888</v>
       </c>
       <c r="G1136" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1136" s="0" t="s">
         <v>16</v>
@@ -43294,7 +43294,7 @@
         <v>1893</v>
       </c>
       <c r="G1139" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1139" s="0" t="s">
         <v>16</v>
@@ -43381,7 +43381,7 @@
         <v>419</v>
       </c>
       <c r="G1142" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1142" s="0" t="s">
         <v>16</v>
@@ -43410,7 +43410,7 @@
         <v>419</v>
       </c>
       <c r="G1143" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1143" s="0" t="s">
         <v>16</v>
@@ -43439,7 +43439,7 @@
         <v>1075</v>
       </c>
       <c r="G1144" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1144" s="0" t="s">
         <v>16</v>
@@ -43671,7 +43671,7 @@
         <v>1909</v>
       </c>
       <c r="G1152" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1152" s="0" t="s">
         <v>16</v>
@@ -43758,7 +43758,7 @@
         <v>1914</v>
       </c>
       <c r="G1155" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1155" s="0" t="s">
         <v>16</v>
@@ -43816,7 +43816,7 @@
         <v>1917</v>
       </c>
       <c r="G1157" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1157" s="0" t="s">
         <v>16</v>
@@ -43845,7 +43845,7 @@
         <v>1918</v>
       </c>
       <c r="G1158" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1158" s="0" t="s">
         <v>16</v>
@@ -43874,7 +43874,7 @@
         <v>322</v>
       </c>
       <c r="G1159" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1159" s="0" t="s">
         <v>16</v>
@@ -44135,7 +44135,7 @@
         <v>1932</v>
       </c>
       <c r="G1168" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1168" s="0" t="s">
         <v>16</v>
@@ -44338,7 +44338,7 @@
         <v>1942</v>
       </c>
       <c r="G1175" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1175" s="0" t="s">
         <v>16</v>
@@ -44454,7 +44454,7 @@
         <v>1947</v>
       </c>
       <c r="G1179" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1179" s="0" t="s">
         <v>16</v>
@@ -44512,7 +44512,7 @@
         <v>1951</v>
       </c>
       <c r="G1181" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1181" s="0" t="s">
         <v>16</v>
@@ -44541,7 +44541,7 @@
         <v>1952</v>
       </c>
       <c r="G1182" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1182" s="0" t="s">
         <v>16</v>
@@ -44599,7 +44599,7 @@
         <v>1955</v>
       </c>
       <c r="G1184" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1184" s="0" t="s">
         <v>16</v>
@@ -44744,7 +44744,7 @@
         <v>1963</v>
       </c>
       <c r="G1189" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1189" s="0" t="s">
         <v>16</v>
@@ -44773,7 +44773,7 @@
         <v>1964</v>
       </c>
       <c r="G1190" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1190" s="0" t="s">
         <v>16</v>
@@ -44802,7 +44802,7 @@
         <v>1965</v>
       </c>
       <c r="G1191" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1191" s="0" t="s">
         <v>16</v>
@@ -44860,7 +44860,7 @@
         <v>1969</v>
       </c>
       <c r="G1193" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1193" s="0" t="s">
         <v>16</v>
@@ -44889,7 +44889,7 @@
         <v>1971</v>
       </c>
       <c r="G1194" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1194" s="0" t="s">
         <v>16</v>
@@ -44918,7 +44918,7 @@
         <v>55</v>
       </c>
       <c r="G1195" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1195" s="0" t="s">
         <v>16</v>
@@ -44947,7 +44947,7 @@
         <v>1974</v>
       </c>
       <c r="G1196" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1196" s="0" t="s">
         <v>16</v>
@@ -44976,7 +44976,7 @@
         <v>1209</v>
       </c>
       <c r="G1197" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1197" s="0" t="s">
         <v>16</v>
@@ -45150,7 +45150,7 @@
         <v>1983</v>
       </c>
       <c r="G1203" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1203" s="0" t="s">
         <v>16</v>
@@ -45411,7 +45411,7 @@
         <v>1992</v>
       </c>
       <c r="G1212" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1212" s="0" t="s">
         <v>16</v>
@@ -45440,7 +45440,7 @@
         <v>1993</v>
       </c>
       <c r="G1213" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1213" s="0" t="s">
         <v>16</v>
@@ -45469,7 +45469,7 @@
         <v>1994</v>
       </c>
       <c r="G1214" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1214" s="0" t="s">
         <v>16</v>
@@ -45788,7 +45788,7 @@
         <v>2012</v>
       </c>
       <c r="G1225" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1225" s="0" t="s">
         <v>16</v>
@@ -45817,7 +45817,7 @@
         <v>1755</v>
       </c>
       <c r="G1226" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1226" s="0" t="s">
         <v>16</v>
@@ -45962,7 +45962,7 @@
         <v>2021</v>
       </c>
       <c r="G1231" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1231" s="0" t="s">
         <v>16</v>
@@ -45991,7 +45991,7 @@
         <v>2022</v>
       </c>
       <c r="G1232" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1232" s="0" t="s">
         <v>16</v>
@@ -46020,7 +46020,7 @@
         <v>2023</v>
       </c>
       <c r="G1233" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1233" s="0" t="s">
         <v>16</v>
@@ -46107,7 +46107,7 @@
         <v>1507</v>
       </c>
       <c r="G1236" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1236" s="0" t="s">
         <v>16</v>
@@ -46165,7 +46165,7 @@
         <v>1917</v>
       </c>
       <c r="G1238" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1238" s="0" t="s">
         <v>16</v>
@@ -46194,7 +46194,7 @@
         <v>1918</v>
       </c>
       <c r="G1239" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1239" s="0" t="s">
         <v>16</v>
@@ -46223,7 +46223,7 @@
         <v>322</v>
       </c>
       <c r="G1240" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1240" s="0" t="s">
         <v>16</v>
@@ -46368,7 +46368,7 @@
         <v>2038</v>
       </c>
       <c r="G1245" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1245" s="0" t="s">
         <v>16</v>
@@ -46484,7 +46484,7 @@
         <v>2044</v>
       </c>
       <c r="G1249" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1249" s="0" t="s">
         <v>16</v>
@@ -46513,7 +46513,7 @@
         <v>2045</v>
       </c>
       <c r="G1250" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1250" s="0" t="s">
         <v>16</v>
@@ -46542,7 +46542,7 @@
         <v>236</v>
       </c>
       <c r="G1251" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1251" s="0" t="s">
         <v>16</v>
@@ -46658,7 +46658,7 @@
         <v>2049</v>
       </c>
       <c r="G1255" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1255" s="0" t="s">
         <v>16</v>
@@ -46687,7 +46687,7 @@
         <v>2044</v>
       </c>
       <c r="G1256" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1256" s="0" t="s">
         <v>16</v>
@@ -46716,7 +46716,7 @@
         <v>2045</v>
       </c>
       <c r="G1257" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1257" s="0" t="s">
         <v>16</v>
@@ -46861,7 +46861,7 @@
         <v>2055</v>
       </c>
       <c r="G1262" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1262" s="0" t="s">
         <v>16</v>
@@ -46890,7 +46890,7 @@
         <v>2057</v>
       </c>
       <c r="G1263" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1263" s="0" t="s">
         <v>16</v>
@@ -46919,7 +46919,7 @@
         <v>2059</v>
       </c>
       <c r="G1264" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1264" s="0" t="s">
         <v>16</v>
@@ -47006,7 +47006,7 @@
         <v>268</v>
       </c>
       <c r="G1267" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1267" s="0" t="s">
         <v>16</v>
@@ -47035,7 +47035,7 @@
         <v>269</v>
       </c>
       <c r="G1268" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1268" s="0" t="s">
         <v>16</v>
@@ -47354,7 +47354,7 @@
         <v>2074</v>
       </c>
       <c r="G1279" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1279" s="0" t="s">
         <v>16</v>
@@ -47673,7 +47673,7 @@
         <v>2090</v>
       </c>
       <c r="G1290" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1290" s="0" t="s">
         <v>16</v>
@@ -47934,7 +47934,7 @@
         <v>2105</v>
       </c>
       <c r="G1299" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1299" s="0" t="s">
         <v>16</v>
@@ -47963,7 +47963,7 @@
         <v>2106</v>
       </c>
       <c r="G1300" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1300" s="0" t="s">
         <v>16</v>
@@ -47992,7 +47992,7 @@
         <v>2108</v>
       </c>
       <c r="G1301" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1301" s="0" t="s">
         <v>16</v>
@@ -48224,7 +48224,7 @@
         <v>2021</v>
       </c>
       <c r="G1309" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1309" s="0" t="s">
         <v>16</v>
@@ -48253,7 +48253,7 @@
         <v>2022</v>
       </c>
       <c r="G1310" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1310" s="0" t="s">
         <v>16</v>
@@ -48282,7 +48282,7 @@
         <v>2023</v>
       </c>
       <c r="G1311" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1311" s="0" t="s">
         <v>16</v>
@@ -48572,7 +48572,7 @@
         <v>1158</v>
       </c>
       <c r="G1321" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1321" s="0" t="s">
         <v>16</v>
@@ -48659,7 +48659,7 @@
         <v>2136</v>
       </c>
       <c r="G1324" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1324" s="0" t="s">
         <v>16</v>
@@ -48746,7 +48746,7 @@
         <v>2139</v>
       </c>
       <c r="G1327" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1327" s="0" t="s">
         <v>16</v>
@@ -48775,7 +48775,7 @@
         <v>225</v>
       </c>
       <c r="G1328" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1328" s="0" t="s">
         <v>16</v>
@@ -48949,7 +48949,7 @@
         <v>2148</v>
       </c>
       <c r="G1334" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1334" s="0" t="s">
         <v>16</v>
@@ -49239,7 +49239,7 @@
         <v>514</v>
       </c>
       <c r="G1344" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1344" s="0" t="s">
         <v>16</v>
@@ -49268,7 +49268,7 @@
         <v>358</v>
       </c>
       <c r="G1345" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1345" s="0" t="s">
         <v>16</v>
@@ -49297,7 +49297,7 @@
         <v>1067</v>
       </c>
       <c r="G1346" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1346" s="0" t="s">
         <v>16</v>
@@ -49355,7 +49355,7 @@
         <v>2160</v>
       </c>
       <c r="G1348" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1348" s="0" t="s">
         <v>16</v>
@@ -49674,7 +49674,7 @@
         <v>2178</v>
       </c>
       <c r="G1359" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1359" s="0" t="s">
         <v>16</v>
@@ -49732,7 +49732,7 @@
         <v>2180</v>
       </c>
       <c r="G1361" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1361" s="0" t="s">
         <v>16</v>
@@ -49761,7 +49761,7 @@
         <v>2182</v>
       </c>
       <c r="G1362" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1362" s="0" t="s">
         <v>16</v>
@@ -49790,7 +49790,7 @@
         <v>2183</v>
       </c>
       <c r="G1363" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1363" s="0" t="s">
         <v>16</v>
@@ -49819,7 +49819,7 @@
         <v>2184</v>
       </c>
       <c r="G1364" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1364" s="0" t="s">
         <v>16</v>
@@ -49935,7 +49935,7 @@
         <v>1351</v>
       </c>
       <c r="G1368" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1368" s="0" t="s">
         <v>16</v>
@@ -50051,7 +50051,7 @@
         <v>427</v>
       </c>
       <c r="G1372" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1372" s="0" t="s">
         <v>16</v>
@@ -50080,7 +50080,7 @@
         <v>429</v>
       </c>
       <c r="G1373" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1373" s="0" t="s">
         <v>16</v>
@@ -50602,7 +50602,7 @@
         <v>2217</v>
       </c>
       <c r="G1391" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1391" s="0" t="s">
         <v>16</v>
@@ -50660,7 +50660,7 @@
         <v>2221</v>
       </c>
       <c r="G1393" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1393" s="0" t="s">
         <v>16</v>
@@ -50805,7 +50805,7 @@
         <v>2227</v>
       </c>
       <c r="G1398" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1398" s="0" t="s">
         <v>16</v>
@@ -50834,7 +50834,7 @@
         <v>2229</v>
       </c>
       <c r="G1399" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1399" s="0" t="s">
         <v>16</v>
@@ -50863,7 +50863,7 @@
         <v>2230</v>
       </c>
       <c r="G1400" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1400" s="0" t="s">
         <v>16</v>
@@ -50892,7 +50892,7 @@
         <v>2231</v>
       </c>
       <c r="G1401" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1401" s="0" t="s">
         <v>16</v>
@@ -50921,7 +50921,7 @@
         <v>707</v>
       </c>
       <c r="G1402" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1402" s="0" t="s">
         <v>16</v>
@@ -50950,7 +50950,7 @@
         <v>2234</v>
       </c>
       <c r="G1403" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1403" s="0" t="s">
         <v>16</v>
@@ -51182,7 +51182,7 @@
         <v>2244</v>
       </c>
       <c r="G1411" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1411" s="0" t="s">
         <v>16</v>
@@ -51443,7 +51443,7 @@
         <v>2258</v>
       </c>
       <c r="G1420" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1420" s="0" t="s">
         <v>16</v>
@@ -51472,7 +51472,7 @@
         <v>301</v>
       </c>
       <c r="G1421" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1421" s="0" t="s">
         <v>16</v>
@@ -51501,7 +51501,7 @@
         <v>303</v>
       </c>
       <c r="G1422" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1422" s="0" t="s">
         <v>16</v>
@@ -51530,7 +51530,7 @@
         <v>305</v>
       </c>
       <c r="G1423" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1423" s="0" t="s">
         <v>16</v>
@@ -51704,7 +51704,7 @@
         <v>513</v>
       </c>
       <c r="G1429" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1429" s="0" t="s">
         <v>16</v>
@@ -51733,7 +51733,7 @@
         <v>514</v>
       </c>
       <c r="G1430" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1430" s="0" t="s">
         <v>16</v>
@@ -51820,7 +51820,7 @@
         <v>2270</v>
       </c>
       <c r="G1433" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1433" s="0" t="s">
         <v>16</v>
@@ -51878,7 +51878,7 @@
         <v>2146</v>
       </c>
       <c r="G1435" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1435" s="0" t="s">
         <v>16</v>
@@ -51936,7 +51936,7 @@
         <v>513</v>
       </c>
       <c r="G1437" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1437" s="0" t="s">
         <v>16</v>
@@ -51965,7 +51965,7 @@
         <v>514</v>
       </c>
       <c r="G1438" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1438" s="0" t="s">
         <v>16</v>
@@ -52110,7 +52110,7 @@
         <v>2164</v>
       </c>
       <c r="G1443" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1443" s="0" t="s">
         <v>16</v>
@@ -52255,7 +52255,7 @@
         <v>1534</v>
       </c>
       <c r="G1448" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1448" s="0" t="s">
         <v>16</v>
@@ -52342,7 +52342,7 @@
         <v>2294</v>
       </c>
       <c r="G1451" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1451" s="0" t="s">
         <v>16</v>
@@ -52371,7 +52371,7 @@
         <v>687</v>
       </c>
       <c r="G1452" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1452" s="0" t="s">
         <v>16</v>
@@ -52400,7 +52400,7 @@
         <v>314</v>
       </c>
       <c r="G1453" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1453" s="0" t="s">
         <v>16</v>
@@ -52516,7 +52516,7 @@
         <v>2300</v>
       </c>
       <c r="G1457" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1457" s="0" t="s">
         <v>16</v>
@@ -52545,7 +52545,7 @@
         <v>290</v>
       </c>
       <c r="G1458" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1458" s="0" t="s">
         <v>16</v>
@@ -52632,7 +52632,7 @@
         <v>2306</v>
       </c>
       <c r="G1461" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1461" s="0" t="s">
         <v>16</v>
@@ -52893,7 +52893,7 @@
         <v>1921</v>
       </c>
       <c r="G1470" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1470" s="0" t="s">
         <v>16</v>
@@ -52922,7 +52922,7 @@
         <v>1922</v>
       </c>
       <c r="G1471" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1471" s="0" t="s">
         <v>16</v>
@@ -53067,7 +53067,7 @@
         <v>238</v>
       </c>
       <c r="G1476" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1476" s="0" t="s">
         <v>16</v>
@@ -53096,7 +53096,7 @@
         <v>2324</v>
       </c>
       <c r="G1477" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1477" s="0" t="s">
         <v>16</v>
@@ -53183,7 +53183,7 @@
         <v>2329</v>
       </c>
       <c r="G1480" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1480" s="0" t="s">
         <v>16</v>
@@ -53415,7 +53415,7 @@
         <v>2338</v>
       </c>
       <c r="G1488" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1488" s="0" t="s">
         <v>16</v>
@@ -53560,7 +53560,7 @@
         <v>2344</v>
       </c>
       <c r="G1493" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1493" s="0" t="s">
         <v>16</v>
@@ -53618,7 +53618,7 @@
         <v>2347</v>
       </c>
       <c r="G1495" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1495" s="0" t="s">
         <v>16</v>
@@ -53647,7 +53647,7 @@
         <v>588</v>
       </c>
       <c r="G1496" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1496" s="0" t="s">
         <v>16</v>
@@ -53676,7 +53676,7 @@
         <v>567</v>
       </c>
       <c r="G1497" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1497" s="0" t="s">
         <v>16</v>
@@ -53705,7 +53705,7 @@
         <v>1632</v>
       </c>
       <c r="G1498" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1498" s="0" t="s">
         <v>16</v>
@@ -54082,7 +54082,7 @@
         <v>2366</v>
       </c>
       <c r="G1511" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1511" s="0" t="s">
         <v>16</v>
@@ -54111,7 +54111,7 @@
         <v>2367</v>
       </c>
       <c r="G1512" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1512" s="0" t="s">
         <v>16</v>
@@ -54140,7 +54140,7 @@
         <v>2368</v>
       </c>
       <c r="G1513" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1513" s="0" t="s">
         <v>16</v>
@@ -54227,7 +54227,7 @@
         <v>2373</v>
       </c>
       <c r="G1516" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1516" s="0" t="s">
         <v>16</v>
@@ -54256,7 +54256,7 @@
         <v>2374</v>
       </c>
       <c r="G1517" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1517" s="0" t="s">
         <v>16</v>
@@ -54285,7 +54285,7 @@
         <v>690</v>
       </c>
       <c r="G1518" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1518" s="0" t="s">
         <v>16</v>
@@ -54314,7 +54314,7 @@
         <v>2377</v>
       </c>
       <c r="G1519" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1519" s="0" t="s">
         <v>16</v>
@@ -54401,7 +54401,7 @@
         <v>1409</v>
       </c>
       <c r="G1522" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1522" s="0" t="s">
         <v>16</v>
@@ -54430,7 +54430,7 @@
         <v>2383</v>
       </c>
       <c r="G1523" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1523" s="0" t="s">
         <v>16</v>
@@ -54459,7 +54459,7 @@
         <v>2383</v>
       </c>
       <c r="G1524" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1524" s="0" t="s">
         <v>16</v>
@@ -54488,7 +54488,7 @@
         <v>2383</v>
       </c>
       <c r="G1525" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1525" s="0" t="s">
         <v>16</v>
@@ -54517,7 +54517,7 @@
         <v>2383</v>
       </c>
       <c r="G1526" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1526" s="0" t="s">
         <v>16</v>
@@ -54604,7 +54604,7 @@
         <v>2390</v>
       </c>
       <c r="G1529" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1529" s="0" t="s">
         <v>16</v>
@@ -55010,7 +55010,7 @@
         <v>2407</v>
       </c>
       <c r="G1543" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1543" s="0" t="s">
         <v>16</v>
@@ -55213,7 +55213,7 @@
         <v>473</v>
       </c>
       <c r="G1550" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1550" s="0" t="s">
         <v>16</v>
@@ -55387,7 +55387,7 @@
         <v>1075</v>
       </c>
       <c r="G1556" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1556" s="0" t="s">
         <v>16</v>
@@ -55503,7 +55503,7 @@
         <v>779</v>
       </c>
       <c r="G1560" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1560" s="0" t="s">
         <v>16</v>
@@ -55561,7 +55561,7 @@
         <v>2430</v>
       </c>
       <c r="G1562" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1562" s="0" t="s">
         <v>16</v>
@@ -55590,7 +55590,7 @@
         <v>2431</v>
       </c>
       <c r="G1563" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1563" s="0" t="s">
         <v>16</v>
@@ -55619,7 +55619,7 @@
         <v>2432</v>
       </c>
       <c r="G1564" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1564" s="0" t="s">
         <v>16</v>
@@ -55706,7 +55706,7 @@
         <v>513</v>
       </c>
       <c r="G1567" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1567" s="0" t="s">
         <v>16</v>
@@ -55735,7 +55735,7 @@
         <v>514</v>
       </c>
       <c r="G1568" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1568" s="0" t="s">
         <v>16</v>
@@ -55764,7 +55764,7 @@
         <v>2436</v>
       </c>
       <c r="G1569" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1569" s="0" t="s">
         <v>16</v>
@@ -55880,7 +55880,7 @@
         <v>2407</v>
       </c>
       <c r="G1573" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1573" s="0" t="s">
         <v>16</v>
@@ -55938,7 +55938,7 @@
         <v>1142</v>
       </c>
       <c r="G1575" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1575" s="0" t="s">
         <v>16</v>
@@ -56054,7 +56054,7 @@
         <v>2449</v>
       </c>
       <c r="G1579" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1579" s="0" t="s">
         <v>16</v>
@@ -56083,7 +56083,7 @@
         <v>2451</v>
       </c>
       <c r="G1580" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1580" s="0" t="s">
         <v>16</v>
@@ -56286,7 +56286,7 @@
         <v>513</v>
       </c>
       <c r="G1587" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1587" s="0" t="s">
         <v>16</v>
@@ -56402,7 +56402,7 @@
         <v>690</v>
       </c>
       <c r="G1591" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1591" s="0" t="s">
         <v>16</v>
@@ -56518,7 +56518,7 @@
         <v>2469</v>
       </c>
       <c r="G1595" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1595" s="0" t="s">
         <v>16</v>
@@ -56663,7 +56663,7 @@
         <v>2473</v>
       </c>
       <c r="G1600" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1600" s="0" t="s">
         <v>16</v>
@@ -56692,7 +56692,7 @@
         <v>2474</v>
       </c>
       <c r="G1601" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1601" s="0" t="s">
         <v>16</v>
@@ -56721,7 +56721,7 @@
         <v>2475</v>
       </c>
       <c r="G1602" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1602" s="0" t="s">
         <v>16</v>
@@ -56779,7 +56779,7 @@
         <v>2479</v>
       </c>
       <c r="G1604" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1604" s="0" t="s">
         <v>16</v>
@@ -56808,7 +56808,7 @@
         <v>2481</v>
       </c>
       <c r="G1605" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1605" s="0" t="s">
         <v>16</v>
@@ -56837,7 +56837,7 @@
         <v>2482</v>
       </c>
       <c r="G1606" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1606" s="0" t="s">
         <v>16</v>
@@ -56866,7 +56866,7 @@
         <v>2484</v>
       </c>
       <c r="G1607" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1607" s="0" t="s">
         <v>16</v>
@@ -56895,7 +56895,7 @@
         <v>2485</v>
       </c>
       <c r="G1608" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1608" s="0" t="s">
         <v>16</v>
@@ -56924,7 +56924,7 @@
         <v>2486</v>
       </c>
       <c r="G1609" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1609" s="0" t="s">
         <v>16</v>
@@ -56953,7 +56953,7 @@
         <v>2488</v>
       </c>
       <c r="G1610" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1610" s="0" t="s">
         <v>16</v>
@@ -56982,7 +56982,7 @@
         <v>2489</v>
       </c>
       <c r="G1611" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1611" s="0" t="s">
         <v>16</v>
@@ -57011,7 +57011,7 @@
         <v>2490</v>
       </c>
       <c r="G1612" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1612" s="0" t="s">
         <v>16</v>
@@ -57040,7 +57040,7 @@
         <v>2084</v>
       </c>
       <c r="G1613" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1613" s="0" t="s">
         <v>16</v>
@@ -57069,7 +57069,7 @@
         <v>1649</v>
       </c>
       <c r="G1614" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1614" s="0" t="s">
         <v>16</v>
@@ -57156,7 +57156,7 @@
         <v>2494</v>
       </c>
       <c r="G1617" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1617" s="0" t="s">
         <v>16</v>
@@ -57214,7 +57214,7 @@
         <v>2498</v>
       </c>
       <c r="G1619" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1619" s="0" t="s">
         <v>16</v>
@@ -57301,7 +57301,7 @@
         <v>2503</v>
       </c>
       <c r="G1622" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1622" s="0" t="s">
         <v>16</v>
@@ -57330,7 +57330,7 @@
         <v>2503</v>
       </c>
       <c r="G1623" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1623" s="0" t="s">
         <v>16</v>
@@ -57359,7 +57359,7 @@
         <v>2503</v>
       </c>
       <c r="G1624" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1624" s="0" t="s">
         <v>16</v>
@@ -57388,7 +57388,7 @@
         <v>2505</v>
       </c>
       <c r="G1625" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1625" s="0" t="s">
         <v>16</v>
@@ -57533,7 +57533,7 @@
         <v>2513</v>
       </c>
       <c r="G1630" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1630" s="0" t="s">
         <v>16</v>
@@ -57678,7 +57678,7 @@
         <v>2160</v>
       </c>
       <c r="G1635" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1635" s="0" t="s">
         <v>16</v>
@@ -57736,7 +57736,7 @@
         <v>2524</v>
       </c>
       <c r="G1637" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1637" s="0" t="s">
         <v>16</v>
@@ -57765,7 +57765,7 @@
         <v>2525</v>
       </c>
       <c r="G1638" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1638" s="0" t="s">
         <v>16</v>
@@ -57881,7 +57881,7 @@
         <v>2530</v>
       </c>
       <c r="G1642" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1642" s="0" t="s">
         <v>16</v>
@@ -57939,7 +57939,7 @@
         <v>2534</v>
       </c>
       <c r="G1644" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1644" s="0" t="s">
         <v>16</v>
@@ -57997,7 +57997,7 @@
         <v>202</v>
       </c>
       <c r="G1646" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1646" s="0" t="s">
         <v>16</v>
@@ -58026,7 +58026,7 @@
         <v>203</v>
       </c>
       <c r="G1647" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1647" s="0" t="s">
         <v>16</v>
@@ -58055,7 +58055,7 @@
         <v>205</v>
       </c>
       <c r="G1648" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1648" s="0" t="s">
         <v>16</v>
@@ -58200,7 +58200,7 @@
         <v>2544</v>
       </c>
       <c r="G1653" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1653" s="0" t="s">
         <v>16</v>
@@ -58258,7 +58258,7 @@
         <v>2548</v>
       </c>
       <c r="G1655" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1655" s="0" t="s">
         <v>16</v>
@@ -58287,7 +58287,7 @@
         <v>2549</v>
       </c>
       <c r="G1656" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1656" s="0" t="s">
         <v>16</v>
@@ -58316,7 +58316,7 @@
         <v>2550</v>
       </c>
       <c r="G1657" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1657" s="0" t="s">
         <v>16</v>
@@ -58432,7 +58432,7 @@
         <v>2557</v>
       </c>
       <c r="G1661" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1661" s="0" t="s">
         <v>16</v>
@@ -58461,7 +58461,7 @@
         <v>2558</v>
       </c>
       <c r="G1662" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1662" s="0" t="s">
         <v>16</v>
@@ -58490,7 +58490,7 @@
         <v>2559</v>
       </c>
       <c r="G1663" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1663" s="0" t="s">
         <v>16</v>
@@ -58519,7 +58519,7 @@
         <v>788</v>
       </c>
       <c r="G1664" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1664" s="0" t="s">
         <v>16</v>
@@ -58606,7 +58606,7 @@
         <v>2565</v>
       </c>
       <c r="G1667" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1667" s="0" t="s">
         <v>16</v>
@@ -58635,7 +58635,7 @@
         <v>2567</v>
       </c>
       <c r="G1668" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1668" s="0" t="s">
         <v>16</v>
@@ -58693,7 +58693,7 @@
         <v>1158</v>
       </c>
       <c r="G1670" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1670" s="0" t="s">
         <v>16</v>
@@ -58896,7 +58896,7 @@
         <v>2575</v>
       </c>
       <c r="G1677" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1677" s="0" t="s">
         <v>16</v>
@@ -58925,7 +58925,7 @@
         <v>1514</v>
       </c>
       <c r="G1678" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1678" s="0" t="s">
         <v>16</v>
@@ -59244,7 +59244,7 @@
         <v>2588</v>
       </c>
       <c r="G1689" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1689" s="0" t="s">
         <v>16</v>
@@ -59418,7 +59418,7 @@
         <v>1632</v>
       </c>
       <c r="G1695" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1695" s="0" t="s">
         <v>16</v>
@@ -59998,7 +59998,7 @@
         <v>1670</v>
       </c>
       <c r="G1715" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1715" s="0" t="s">
         <v>16</v>
@@ -60172,7 +60172,7 @@
         <v>1728</v>
       </c>
       <c r="G1721" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1721" s="0" t="s">
         <v>16</v>
@@ -60201,7 +60201,7 @@
         <v>1729</v>
       </c>
       <c r="G1722" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1722" s="0" t="s">
         <v>16</v>
@@ -60230,7 +60230,7 @@
         <v>1730</v>
       </c>
       <c r="G1723" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1723" s="0" t="s">
         <v>16</v>
@@ -60259,7 +60259,7 @@
         <v>2624</v>
       </c>
       <c r="G1724" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1724" s="0" t="s">
         <v>16</v>
@@ -60578,7 +60578,7 @@
         <v>2635</v>
       </c>
       <c r="G1735" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1735" s="0" t="s">
         <v>16</v>
@@ -60723,7 +60723,7 @@
         <v>2644</v>
       </c>
       <c r="G1740" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1740" s="0" t="s">
         <v>16</v>
@@ -60810,7 +60810,7 @@
         <v>2648</v>
       </c>
       <c r="G1743" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1743" s="0" t="s">
         <v>16</v>
@@ -60839,7 +60839,7 @@
         <v>2649</v>
       </c>
       <c r="G1744" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1744" s="0" t="s">
         <v>16</v>
@@ -60868,7 +60868,7 @@
         <v>2650</v>
       </c>
       <c r="G1745" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1745" s="0" t="s">
         <v>16</v>
@@ -60897,7 +60897,7 @@
         <v>2652</v>
       </c>
       <c r="G1746" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1746" s="0" t="s">
         <v>16</v>
@@ -60926,7 +60926,7 @@
         <v>2653</v>
       </c>
       <c r="G1747" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1747" s="0" t="s">
         <v>16</v>
@@ -60955,7 +60955,7 @@
         <v>2654</v>
       </c>
       <c r="G1748" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1748" s="0" t="s">
         <v>16</v>
@@ -61042,7 +61042,7 @@
         <v>671</v>
       </c>
       <c r="G1751" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1751" s="0" t="s">
         <v>16</v>
@@ -61158,7 +61158,7 @@
         <v>1230</v>
       </c>
       <c r="G1755" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1755" s="0" t="s">
         <v>16</v>
@@ -61303,7 +61303,7 @@
         <v>1712</v>
       </c>
       <c r="G1760" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1760" s="0" t="s">
         <v>16</v>
@@ -61332,7 +61332,7 @@
         <v>1376</v>
       </c>
       <c r="G1761" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1761" s="0" t="s">
         <v>16</v>
@@ -61390,7 +61390,7 @@
         <v>606</v>
       </c>
       <c r="G1763" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1763" s="0" t="s">
         <v>16</v>
@@ -61419,7 +61419,7 @@
         <v>2673</v>
       </c>
       <c r="G1764" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1764" s="0" t="s">
         <v>16</v>
@@ -61448,7 +61448,7 @@
         <v>2673</v>
       </c>
       <c r="G1765" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1765" s="0" t="s">
         <v>16</v>
@@ -61477,7 +61477,7 @@
         <v>2673</v>
       </c>
       <c r="G1766" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1766" s="0" t="s">
         <v>16</v>
@@ -61564,7 +61564,7 @@
         <v>519</v>
       </c>
       <c r="G1769" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1769" s="0" t="s">
         <v>16</v>
@@ -61593,7 +61593,7 @@
         <v>520</v>
       </c>
       <c r="G1770" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1770" s="0" t="s">
         <v>16</v>
@@ -61651,7 +61651,7 @@
         <v>1721</v>
       </c>
       <c r="G1772" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1772" s="0" t="s">
         <v>16</v>
@@ -61680,7 +61680,7 @@
         <v>1722</v>
       </c>
       <c r="G1773" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1773" s="0" t="s">
         <v>16</v>
@@ -61709,7 +61709,7 @@
         <v>1723</v>
       </c>
       <c r="G1774" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1774" s="0" t="s">
         <v>16</v>
@@ -61825,7 +61825,7 @@
         <v>441</v>
       </c>
       <c r="G1778" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1778" s="0" t="s">
         <v>16</v>
@@ -61854,7 +61854,7 @@
         <v>374</v>
       </c>
       <c r="G1779" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1779" s="0" t="s">
         <v>16</v>
@@ -61912,7 +61912,7 @@
         <v>314</v>
       </c>
       <c r="G1781" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1781" s="0" t="s">
         <v>16</v>
@@ -62028,7 +62028,7 @@
         <v>1917</v>
       </c>
       <c r="G1785" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1785" s="0" t="s">
         <v>16</v>
@@ -62057,7 +62057,7 @@
         <v>1918</v>
       </c>
       <c r="G1786" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1786" s="0" t="s">
         <v>16</v>
@@ -62086,7 +62086,7 @@
         <v>322</v>
       </c>
       <c r="G1787" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1787" s="0" t="s">
         <v>16</v>
@@ -62115,7 +62115,7 @@
         <v>598</v>
       </c>
       <c r="G1788" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1788" s="0" t="s">
         <v>16</v>
@@ -62202,7 +62202,7 @@
         <v>520</v>
       </c>
       <c r="G1791" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1791" s="0" t="s">
         <v>16</v>
@@ -62231,7 +62231,7 @@
         <v>521</v>
       </c>
       <c r="G1792" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1792" s="0" t="s">
         <v>16</v>
@@ -62260,7 +62260,7 @@
         <v>519</v>
       </c>
       <c r="G1793" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1793" s="0" t="s">
         <v>16</v>
@@ -62289,7 +62289,7 @@
         <v>1209</v>
       </c>
       <c r="G1794" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1794" s="0" t="s">
         <v>16</v>
@@ -62318,7 +62318,7 @@
         <v>47</v>
       </c>
       <c r="G1795" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1795" s="0" t="s">
         <v>16</v>
@@ -62347,7 +62347,7 @@
         <v>2697</v>
       </c>
       <c r="G1796" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1796" s="0" t="s">
         <v>16</v>
@@ -62376,7 +62376,7 @@
         <v>2698</v>
       </c>
       <c r="G1797" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1797" s="0" t="s">
         <v>16</v>
@@ -62521,7 +62521,7 @@
         <v>2707</v>
       </c>
       <c r="G1802" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1802" s="0" t="s">
         <v>16</v>
@@ -62550,7 +62550,7 @@
         <v>2708</v>
       </c>
       <c r="G1803" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1803" s="0" t="s">
         <v>16</v>
@@ -62608,7 +62608,7 @@
         <v>2712</v>
       </c>
       <c r="G1805" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1805" s="0" t="s">
         <v>16</v>
@@ -62695,7 +62695,7 @@
         <v>2338</v>
       </c>
       <c r="G1808" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1808" s="0" t="s">
         <v>16</v>
@@ -63043,7 +63043,7 @@
         <v>2723</v>
       </c>
       <c r="G1820" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1820" s="0" t="s">
         <v>16</v>
@@ -63246,7 +63246,7 @@
         <v>2734</v>
       </c>
       <c r="G1827" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1827" s="0" t="s">
         <v>16</v>
@@ -63275,7 +63275,7 @@
         <v>2735</v>
       </c>
       <c r="G1828" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1828" s="0" t="s">
         <v>16</v>
@@ -63304,7 +63304,7 @@
         <v>2737</v>
       </c>
       <c r="G1829" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1829" s="0" t="s">
         <v>16</v>
@@ -63362,7 +63362,7 @@
         <v>976</v>
       </c>
       <c r="G1831" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1831" s="0" t="s">
         <v>16</v>
@@ -63391,7 +63391,7 @@
         <v>2044</v>
       </c>
       <c r="G1832" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1832" s="0" t="s">
         <v>16</v>
@@ -63420,7 +63420,7 @@
         <v>2045</v>
       </c>
       <c r="G1833" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1833" s="0" t="s">
         <v>16</v>
@@ -63449,7 +63449,7 @@
         <v>236</v>
       </c>
       <c r="G1834" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1834" s="0" t="s">
         <v>16</v>
@@ -63826,7 +63826,7 @@
         <v>2754</v>
       </c>
       <c r="G1847" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1847" s="0" t="s">
         <v>16</v>
@@ -63855,7 +63855,7 @@
         <v>1712</v>
       </c>
       <c r="G1848" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1848" s="0" t="s">
         <v>16</v>
@@ -63884,7 +63884,7 @@
         <v>2757</v>
       </c>
       <c r="G1849" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1849" s="0" t="s">
         <v>16</v>
@@ -63942,7 +63942,7 @@
         <v>2760</v>
       </c>
       <c r="G1851" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1851" s="0" t="s">
         <v>16</v>
@@ -63971,7 +63971,7 @@
         <v>2762</v>
       </c>
       <c r="G1852" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1852" s="0" t="s">
         <v>16</v>
@@ -64058,7 +64058,7 @@
         <v>1888</v>
       </c>
       <c r="G1855" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1855" s="0" t="s">
         <v>16</v>
@@ -64087,7 +64087,7 @@
         <v>1029</v>
       </c>
       <c r="G1856" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1856" s="0" t="s">
         <v>16</v>
@@ -64116,7 +64116,7 @@
         <v>1030</v>
       </c>
       <c r="G1857" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1857" s="0" t="s">
         <v>16</v>
@@ -64203,7 +64203,7 @@
         <v>2772</v>
       </c>
       <c r="G1860" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1860" s="0" t="s">
         <v>16</v>
@@ -64261,7 +64261,7 @@
         <v>2775</v>
       </c>
       <c r="G1862" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1862" s="0" t="s">
         <v>16</v>
@@ -64290,7 +64290,7 @@
         <v>322</v>
       </c>
       <c r="G1863" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1863" s="0" t="s">
         <v>16</v>
@@ -64406,7 +64406,7 @@
         <v>1194</v>
       </c>
       <c r="G1867" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1867" s="0" t="s">
         <v>16</v>
@@ -64435,7 +64435,7 @@
         <v>2784</v>
       </c>
       <c r="G1868" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1868" s="0" t="s">
         <v>16</v>
@@ -64464,7 +64464,7 @@
         <v>1207</v>
       </c>
       <c r="G1869" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1869" s="0" t="s">
         <v>16</v>
@@ -64609,7 +64609,7 @@
         <v>445</v>
       </c>
       <c r="G1874" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1874" s="0" t="s">
         <v>16</v>
@@ -64638,7 +64638,7 @@
         <v>2790</v>
       </c>
       <c r="G1875" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1875" s="0" t="s">
         <v>16</v>
@@ -64667,7 +64667,7 @@
         <v>2792</v>
       </c>
       <c r="G1876" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1876" s="0" t="s">
         <v>16</v>
@@ -64696,7 +64696,7 @@
         <v>2793</v>
       </c>
       <c r="G1877" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1877" s="0" t="s">
         <v>16</v>
@@ -64754,7 +64754,7 @@
         <v>464</v>
       </c>
       <c r="G1879" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1879" s="0" t="s">
         <v>16</v>
@@ -64783,7 +64783,7 @@
         <v>1295</v>
       </c>
       <c r="G1880" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1880" s="0" t="s">
         <v>16</v>
@@ -64957,7 +64957,7 @@
         <v>2805</v>
       </c>
       <c r="G1886" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1886" s="0" t="s">
         <v>16</v>
@@ -65044,7 +65044,7 @@
         <v>2811</v>
       </c>
       <c r="G1889" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H1889" s="0" t="s">
         <v>16</v>
@@ -65073,7 +65073,7 @@
         <v>2813</v>
       </c>
       <c r="G1890" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1890" s="0" t="s">
         <v>16</v>
@@ -65102,7 +65102,7 @@
         <v>322</v>
       </c>
       <c r="G1891" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1891" s="0" t="s">
         <v>16</v>
@@ -65160,7 +65160,7 @@
         <v>2820</v>
       </c>
       <c r="G1893" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1893" s="0" t="s">
         <v>16</v>
@@ -65247,7 +65247,7 @@
         <v>2825</v>
       </c>
       <c r="G1896" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1896" s="0" t="s">
         <v>16</v>
@@ -65334,7 +65334,7 @@
         <v>2829</v>
       </c>
       <c r="G1899" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1899" s="0" t="s">
         <v>16</v>
@@ -65421,7 +65421,7 @@
         <v>2833</v>
       </c>
       <c r="G1902" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1902" s="0" t="s">
         <v>16</v>
@@ -65479,7 +65479,7 @@
         <v>2836</v>
       </c>
       <c r="G1904" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1904" s="0" t="s">
         <v>16</v>
@@ -65537,7 +65537,7 @@
         <v>2839</v>
       </c>
       <c r="G1906" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1906" s="0" t="s">
         <v>16</v>
@@ -65595,7 +65595,7 @@
         <v>2842</v>
       </c>
       <c r="G1908" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1908" s="0" t="s">
         <v>16</v>
@@ -65653,7 +65653,7 @@
         <v>2845</v>
       </c>
       <c r="G1910" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1910" s="0" t="s">
         <v>16</v>
@@ -65740,7 +65740,7 @@
         <v>2849</v>
       </c>
       <c r="G1913" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1913" s="0" t="s">
         <v>16</v>
@@ -65827,7 +65827,7 @@
         <v>2853</v>
       </c>
       <c r="G1916" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1916" s="0" t="s">
         <v>16</v>
@@ -65914,7 +65914,7 @@
         <v>2857</v>
       </c>
       <c r="G1919" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1919" s="0" t="s">
         <v>16</v>
@@ -66001,7 +66001,7 @@
         <v>2861</v>
       </c>
       <c r="G1922" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1922" s="0" t="s">
         <v>16</v>
@@ -66088,7 +66088,7 @@
         <v>2865</v>
       </c>
       <c r="G1925" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1925" s="0" t="s">
         <v>16</v>
@@ -66175,7 +66175,7 @@
         <v>2869</v>
       </c>
       <c r="G1928" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1928" s="0" t="s">
         <v>16</v>
@@ -66262,7 +66262,7 @@
         <v>2873</v>
       </c>
       <c r="G1931" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1931" s="0" t="s">
         <v>16</v>
@@ -66349,7 +66349,7 @@
         <v>2877</v>
       </c>
       <c r="G1934" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1934" s="0" t="s">
         <v>16</v>
@@ -66436,7 +66436,7 @@
         <v>2881</v>
       </c>
       <c r="G1937" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1937" s="0" t="s">
         <v>16</v>
@@ -66523,7 +66523,7 @@
         <v>2885</v>
       </c>
       <c r="G1940" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1940" s="0" t="s">
         <v>16</v>
@@ -66639,7 +66639,7 @@
         <v>2891</v>
       </c>
       <c r="G1944" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1944" s="0" t="s">
         <v>16</v>
@@ -66726,7 +66726,7 @@
         <v>2895</v>
       </c>
       <c r="G1947" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1947" s="0" t="s">
         <v>16</v>
@@ -66784,7 +66784,7 @@
         <v>2898</v>
       </c>
       <c r="G1949" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1949" s="0" t="s">
         <v>16</v>
@@ -66929,7 +66929,7 @@
         <v>2906</v>
       </c>
       <c r="G1954" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1954" s="0" t="s">
         <v>16</v>
@@ -67074,7 +67074,7 @@
         <v>2913</v>
       </c>
       <c r="G1959" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1959" s="0" t="s">
         <v>16</v>
@@ -67161,7 +67161,7 @@
         <v>2917</v>
       </c>
       <c r="G1962" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1962" s="0" t="s">
         <v>16</v>
@@ -67219,7 +67219,7 @@
         <v>2919</v>
       </c>
       <c r="G1964" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1964" s="0" t="s">
         <v>16</v>
@@ -67277,7 +67277,7 @@
         <v>2922</v>
       </c>
       <c r="G1966" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1966" s="0" t="s">
         <v>16</v>
@@ -67364,7 +67364,7 @@
         <v>2926</v>
       </c>
       <c r="G1969" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1969" s="0" t="s">
         <v>16</v>
@@ -67422,7 +67422,7 @@
         <v>2928</v>
       </c>
       <c r="G1971" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1971" s="0" t="s">
         <v>16</v>
@@ -67480,7 +67480,7 @@
         <v>2931</v>
       </c>
       <c r="G1973" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1973" s="0" t="s">
         <v>16</v>
@@ -67567,7 +67567,7 @@
         <v>2935</v>
       </c>
       <c r="G1976" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1976" s="0" t="s">
         <v>16</v>
@@ -67654,7 +67654,7 @@
         <v>2939</v>
       </c>
       <c r="G1979" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1979" s="0" t="s">
         <v>16</v>
@@ -67741,7 +67741,7 @@
         <v>2943</v>
       </c>
       <c r="G1982" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1982" s="0" t="s">
         <v>16</v>
@@ -67799,7 +67799,7 @@
         <v>2946</v>
       </c>
       <c r="G1984" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1984" s="0" t="s">
         <v>16</v>
@@ -67857,7 +67857,7 @@
         <v>2949</v>
       </c>
       <c r="G1986" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1986" s="0" t="s">
         <v>16</v>
@@ -67944,7 +67944,7 @@
         <v>2953</v>
       </c>
       <c r="G1989" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1989" s="0" t="s">
         <v>16</v>
@@ -68031,7 +68031,7 @@
         <v>2957</v>
       </c>
       <c r="G1992" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1992" s="0" t="s">
         <v>16</v>
@@ -68089,7 +68089,7 @@
         <v>2960</v>
       </c>
       <c r="G1994" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1994" s="0" t="s">
         <v>16</v>
@@ -68176,7 +68176,7 @@
         <v>2964</v>
       </c>
       <c r="G1997" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1997" s="0" t="s">
         <v>16</v>
@@ -68234,7 +68234,7 @@
         <v>2967</v>
       </c>
       <c r="G1999" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1999" s="0" t="s">
         <v>16</v>
@@ -68350,7 +68350,7 @@
         <v>2973</v>
       </c>
       <c r="G2003" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2003" s="0" t="s">
         <v>16</v>
@@ -68437,7 +68437,7 @@
         <v>2977</v>
       </c>
       <c r="G2006" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2006" s="0" t="s">
         <v>16</v>
@@ -68524,7 +68524,7 @@
         <v>2981</v>
       </c>
       <c r="G2009" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2009" s="0" t="s">
         <v>16</v>
@@ -68611,7 +68611,7 @@
         <v>2986</v>
       </c>
       <c r="G2012" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2012" s="0" t="s">
         <v>16</v>
@@ -68669,7 +68669,7 @@
         <v>2988</v>
       </c>
       <c r="G2014" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2014" s="0" t="s">
         <v>16</v>
@@ -68727,7 +68727,7 @@
         <v>2991</v>
       </c>
       <c r="G2016" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2016" s="0" t="s">
         <v>16</v>
@@ -68814,7 +68814,7 @@
         <v>2995</v>
       </c>
       <c r="G2019" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2019" s="0" t="s">
         <v>16</v>
@@ -68901,7 +68901,7 @@
         <v>2999</v>
       </c>
       <c r="G2022" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2022" s="0" t="s">
         <v>16</v>
@@ -68988,7 +68988,7 @@
         <v>3003</v>
       </c>
       <c r="G2025" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2025" s="0" t="s">
         <v>16</v>
@@ -69075,7 +69075,7 @@
         <v>3007</v>
       </c>
       <c r="G2028" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2028" s="0" t="s">
         <v>16</v>
@@ -69133,7 +69133,7 @@
         <v>3010</v>
       </c>
       <c r="G2030" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2030" s="0" t="s">
         <v>16</v>
@@ -69220,7 +69220,7 @@
         <v>3014</v>
       </c>
       <c r="G2033" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2033" s="0" t="s">
         <v>16</v>
@@ -69336,7 +69336,7 @@
         <v>3020</v>
       </c>
       <c r="G2037" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2037" s="0" t="s">
         <v>16</v>
@@ -69394,7 +69394,7 @@
         <v>3023</v>
       </c>
       <c r="G2039" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2039" s="0" t="s">
         <v>16</v>
@@ -69481,7 +69481,7 @@
         <v>3027</v>
       </c>
       <c r="G2042" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2042" s="0" t="s">
         <v>16</v>
@@ -69539,7 +69539,7 @@
         <v>3029</v>
       </c>
       <c r="G2044" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2044" s="0" t="s">
         <v>16</v>
@@ -69597,7 +69597,7 @@
         <v>3032</v>
       </c>
       <c r="G2046" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2046" s="0" t="s">
         <v>16</v>
@@ -69684,7 +69684,7 @@
         <v>3036</v>
       </c>
       <c r="G2049" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2049" s="0" t="s">
         <v>16</v>
@@ -69771,7 +69771,7 @@
         <v>3040</v>
       </c>
       <c r="G2052" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2052" s="0" t="s">
         <v>16</v>
@@ -69858,7 +69858,7 @@
         <v>3044</v>
       </c>
       <c r="G2055" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2055" s="0" t="s">
         <v>16</v>
@@ -69945,7 +69945,7 @@
         <v>3048</v>
       </c>
       <c r="G2058" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2058" s="0" t="s">
         <v>16</v>
@@ -70032,7 +70032,7 @@
         <v>3052</v>
       </c>
       <c r="G2061" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2061" s="0" t="s">
         <v>16</v>
@@ -70119,7 +70119,7 @@
         <v>3056</v>
       </c>
       <c r="G2064" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2064" s="0" t="s">
         <v>16</v>
@@ -70206,7 +70206,7 @@
         <v>3060</v>
       </c>
       <c r="G2067" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2067" s="0" t="s">
         <v>16</v>
@@ -70235,7 +70235,7 @@
         <v>3062</v>
       </c>
       <c r="G2068" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2068" s="0" t="s">
         <v>16</v>
@@ -70264,7 +70264,7 @@
         <v>3064</v>
       </c>
       <c r="G2069" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2069" s="0" t="s">
         <v>16</v>
@@ -70351,7 +70351,7 @@
         <v>3068</v>
       </c>
       <c r="G2072" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2072" s="0" t="s">
         <v>16</v>
@@ -70438,7 +70438,7 @@
         <v>3072</v>
       </c>
       <c r="G2075" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2075" s="0" t="s">
         <v>16</v>
@@ -70467,7 +70467,7 @@
         <v>3074</v>
       </c>
       <c r="G2076" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2076" s="0" t="s">
         <v>16</v>
@@ -70525,7 +70525,7 @@
         <v>3077</v>
       </c>
       <c r="G2078" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2078" s="0" t="s">
         <v>16</v>
@@ -70612,7 +70612,7 @@
         <v>3081</v>
       </c>
       <c r="G2081" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2081" s="0" t="s">
         <v>16</v>
@@ -70670,7 +70670,7 @@
         <v>3083</v>
       </c>
       <c r="G2083" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2083" s="0" t="s">
         <v>16</v>
@@ -70728,7 +70728,7 @@
         <v>3086</v>
       </c>
       <c r="G2085" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2085" s="0" t="s">
         <v>16</v>
@@ -70815,7 +70815,7 @@
         <v>3090</v>
       </c>
       <c r="G2088" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2088" s="0" t="s">
         <v>16</v>
@@ -70902,7 +70902,7 @@
         <v>3094</v>
       </c>
       <c r="G2091" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2091" s="0" t="s">
         <v>16</v>
@@ -71018,7 +71018,7 @@
         <v>3100</v>
       </c>
       <c r="G2095" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2095" s="0" t="s">
         <v>16</v>
@@ -71076,7 +71076,7 @@
         <v>3103</v>
       </c>
       <c r="G2097" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2097" s="0" t="s">
         <v>16</v>
@@ -71279,7 +71279,7 @@
         <v>3113</v>
       </c>
       <c r="G2104" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2104" s="0" t="s">
         <v>16</v>
@@ -71366,7 +71366,7 @@
         <v>3117</v>
       </c>
       <c r="G2107" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2107" s="0" t="s">
         <v>16</v>
@@ -71395,7 +71395,7 @@
         <v>3118</v>
       </c>
       <c r="G2108" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2108" s="0" t="s">
         <v>16</v>
@@ -71424,7 +71424,7 @@
         <v>70</v>
       </c>
       <c r="G2109" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2109" s="0" t="s">
         <v>16</v>
@@ -71482,7 +71482,7 @@
         <v>3121</v>
       </c>
       <c r="G2111" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2111" s="0" t="s">
         <v>16</v>
@@ -71685,7 +71685,7 @@
         <v>1514</v>
       </c>
       <c r="G2118" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2118" s="0" t="s">
         <v>16</v>
@@ -71714,7 +71714,7 @@
         <v>3127</v>
       </c>
       <c r="G2119" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H2119" s="0" t="s">
         <v>16</v>
@@ -71888,7 +71888,7 @@
         <v>3134</v>
       </c>
       <c r="G2125" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2125" s="0" t="s">
         <v>16</v>
@@ -71946,7 +71946,7 @@
         <v>3136</v>
       </c>
       <c r="G2127" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2127" s="0" t="s">
         <v>16</v>
@@ -72033,7 +72033,7 @@
         <v>3140</v>
       </c>
       <c r="G2130" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2130" s="0" t="s">
         <v>16</v>
@@ -72062,7 +72062,7 @@
         <v>3141</v>
       </c>
       <c r="G2131" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2131" s="0" t="s">
         <v>16</v>
@@ -72091,7 +72091,7 @@
         <v>3142</v>
       </c>
       <c r="G2132" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2132" s="0" t="s">
         <v>16</v>
@@ -72149,7 +72149,7 @@
         <v>3144</v>
       </c>
       <c r="G2134" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2134" s="0" t="s">
         <v>16</v>
@@ -72178,7 +72178,7 @@
         <v>3145</v>
       </c>
       <c r="G2135" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2135" s="0" t="s">
         <v>16</v>
@@ -72207,7 +72207,7 @@
         <v>3146</v>
       </c>
       <c r="G2136" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2136" s="0" t="s">
         <v>16</v>
@@ -72236,7 +72236,7 @@
         <v>3147</v>
       </c>
       <c r="G2137" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2137" s="0" t="s">
         <v>16</v>
@@ -72323,7 +72323,7 @@
         <v>3149</v>
       </c>
       <c r="G2140" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2140" s="0" t="s">
         <v>16</v>
@@ -72352,7 +72352,7 @@
         <v>1818</v>
       </c>
       <c r="G2141" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2141" s="0" t="s">
         <v>16</v>
@@ -72381,7 +72381,7 @@
         <v>3151</v>
       </c>
       <c r="G2142" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2142" s="0" t="s">
         <v>16</v>
@@ -72410,7 +72410,7 @@
         <v>3152</v>
       </c>
       <c r="G2143" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2143" s="0" t="s">
         <v>16</v>
@@ -72439,7 +72439,7 @@
         <v>3153</v>
       </c>
       <c r="G2144" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2144" s="0" t="s">
         <v>16</v>
@@ -72468,7 +72468,7 @@
         <v>3155</v>
       </c>
       <c r="G2145" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2145" s="0" t="s">
         <v>16</v>
@@ -72497,7 +72497,7 @@
         <v>3156</v>
       </c>
       <c r="G2146" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2146" s="0" t="s">
         <v>16</v>
@@ -72555,7 +72555,7 @@
         <v>3158</v>
       </c>
       <c r="G2148" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H2148" s="0" t="s">
         <v>16</v>
@@ -72584,7 +72584,7 @@
         <v>3159</v>
       </c>
       <c r="G2149" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2149" s="0" t="s">
         <v>16</v>
@@ -72613,7 +72613,7 @@
         <v>3160</v>
       </c>
       <c r="G2150" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2150" s="0" t="s">
         <v>16</v>
@@ -72642,7 +72642,7 @@
         <v>3161</v>
       </c>
       <c r="G2151" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2151" s="0" t="s">
         <v>16</v>
@@ -72671,7 +72671,7 @@
         <v>3162</v>
       </c>
       <c r="G2152" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2152" s="0" t="s">
         <v>16</v>
@@ -72729,7 +72729,7 @@
         <v>3165</v>
       </c>
       <c r="G2154" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2154" s="0" t="s">
         <v>16</v>
@@ -72758,7 +72758,7 @@
         <v>3166</v>
       </c>
       <c r="G2155" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2155" s="0" t="s">
         <v>16</v>
@@ -72787,7 +72787,7 @@
         <v>3167</v>
       </c>
       <c r="G2156" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2156" s="0" t="s">
         <v>16</v>
@@ -72903,7 +72903,7 @@
         <v>3171</v>
       </c>
       <c r="G2160" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H2160" s="0" t="s">
         <v>16</v>
@@ -73019,7 +73019,7 @@
         <v>3176</v>
       </c>
       <c r="G2164" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2164" s="0" t="s">
         <v>16</v>
@@ -73048,7 +73048,7 @@
         <v>3177</v>
       </c>
       <c r="G2165" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2165" s="0" t="s">
         <v>16</v>
@@ -73077,7 +73077,7 @@
         <v>3178</v>
       </c>
       <c r="G2166" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2166" s="0" t="s">
         <v>16</v>
@@ -73106,7 +73106,7 @@
         <v>3179</v>
       </c>
       <c r="G2167" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2167" s="0" t="s">
         <v>16</v>
@@ -73135,7 +73135,7 @@
         <v>3180</v>
       </c>
       <c r="G2168" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2168" s="0" t="s">
         <v>16</v>
@@ -73280,7 +73280,7 @@
         <v>3185</v>
       </c>
       <c r="G2173" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2173" s="0" t="s">
         <v>16</v>
@@ -73454,7 +73454,7 @@
         <v>3191</v>
       </c>
       <c r="G2179" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2179" s="0" t="s">
         <v>16</v>
@@ -73483,7 +73483,7 @@
         <v>2082</v>
       </c>
       <c r="G2180" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2180" s="0" t="s">
         <v>16</v>
@@ -73512,7 +73512,7 @@
         <v>3192</v>
       </c>
       <c r="G2181" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2181" s="0" t="s">
         <v>16</v>
@@ -73541,7 +73541,7 @@
         <v>3193</v>
       </c>
       <c r="G2182" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2182" s="0" t="s">
         <v>16</v>
@@ -73570,7 +73570,7 @@
         <v>3194</v>
       </c>
       <c r="G2183" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2183" s="0" t="s">
         <v>16</v>
@@ -73599,7 +73599,7 @@
         <v>3195</v>
       </c>
       <c r="G2184" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2184" s="0" t="s">
         <v>16</v>
@@ -73918,7 +73918,7 @@
         <v>2251</v>
       </c>
       <c r="G2195" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2195" s="0" t="s">
         <v>16</v>
@@ -73947,7 +73947,7 @@
         <v>1230</v>
       </c>
       <c r="G2196" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2196" s="0" t="s">
         <v>16</v>
@@ -73976,7 +73976,7 @@
         <v>3207</v>
       </c>
       <c r="G2197" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2197" s="0" t="s">
         <v>16</v>
@@ -74121,7 +74121,7 @@
         <v>3213</v>
       </c>
       <c r="G2202" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2202" s="0" t="s">
         <v>16</v>
@@ -74150,7 +74150,7 @@
         <v>3214</v>
       </c>
       <c r="G2203" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2203" s="0" t="s">
         <v>16</v>
@@ -74208,7 +74208,7 @@
         <v>3216</v>
       </c>
       <c r="G2205" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H2205" s="0" t="s">
         <v>16</v>
@@ -74237,7 +74237,7 @@
         <v>3216</v>
       </c>
       <c r="G2206" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H2206" s="0" t="s">
         <v>16</v>
@@ -74324,7 +74324,7 @@
         <v>3219</v>
       </c>
       <c r="G2209" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2209" s="0" t="s">
         <v>16</v>
@@ -74353,7 +74353,7 @@
         <v>3220</v>
       </c>
       <c r="G2210" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2210" s="0" t="s">
         <v>16</v>
@@ -74382,7 +74382,7 @@
         <v>3221</v>
       </c>
       <c r="G2211" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2211" s="0" t="s">
         <v>16</v>
@@ -74411,7 +74411,7 @@
         <v>3222</v>
       </c>
       <c r="G2212" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2212" s="0" t="s">
         <v>16</v>
@@ -74440,7 +74440,7 @@
         <v>3223</v>
       </c>
       <c r="G2213" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2213" s="0" t="s">
         <v>16</v>
@@ -74469,7 +74469,7 @@
         <v>3224</v>
       </c>
       <c r="G2214" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2214" s="0" t="s">
         <v>16</v>
@@ -74498,7 +74498,7 @@
         <v>3225</v>
       </c>
       <c r="G2215" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2215" s="0" t="s">
         <v>16</v>
@@ -74643,7 +74643,7 @@
         <v>3229</v>
       </c>
       <c r="G2220" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2220" s="0" t="s">
         <v>16</v>
@@ -74730,7 +74730,7 @@
         <v>463</v>
       </c>
       <c r="G2223" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2223" s="0" t="s">
         <v>16</v>
@@ -74759,7 +74759,7 @@
         <v>3232</v>
       </c>
       <c r="G2224" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2224" s="0" t="s">
         <v>16</v>
@@ -74788,7 +74788,7 @@
         <v>3233</v>
       </c>
       <c r="G2225" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2225" s="0" t="s">
         <v>16</v>
@@ -74933,7 +74933,7 @@
         <v>3236</v>
       </c>
       <c r="G2230" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2230" s="0" t="s">
         <v>16</v>
@@ -75020,7 +75020,7 @@
         <v>3239</v>
       </c>
       <c r="G2233" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2233" s="0" t="s">
         <v>16</v>
@@ -75484,7 +75484,7 @@
         <v>3258</v>
       </c>
       <c r="G2249" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2249" s="0" t="s">
         <v>16</v>
@@ -75600,7 +75600,7 @@
         <v>3262</v>
       </c>
       <c r="G2253" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2253" s="0" t="s">
         <v>16</v>
@@ -75629,7 +75629,7 @@
         <v>3263</v>
       </c>
       <c r="G2254" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2254" s="0" t="s">
         <v>16</v>
@@ -75803,7 +75803,7 @@
         <v>3269</v>
       </c>
       <c r="G2260" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2260" s="0" t="s">
         <v>16</v>
@@ -75890,7 +75890,7 @@
         <v>3273</v>
       </c>
       <c r="G2263" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2263" s="0" t="s">
         <v>16</v>
@@ -75948,7 +75948,7 @@
         <v>3275</v>
       </c>
       <c r="G2265" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2265" s="0" t="s">
         <v>16</v>
